--- a/research/traditional_assets/database/data/spain/spain_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_retail_distributors.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.083202787159014</v>
+        <v>0.08302853019111646</v>
       </c>
       <c r="C2">
-        <v>455.0628815459839</v>
+        <v>452.0377034760818</v>
       </c>
       <c r="D2">
-        <v>411.862881545984</v>
+        <v>413.7907034760818</v>
       </c>
       <c r="E2">
-        <v>-372.4</v>
+        <v>-367.447</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.952999999999999</v>
       </c>
       <c r="G2">
         <v>43.2</v>
@@ -1451,28 +1451,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2491359</v>
       </c>
       <c r="N2">
-        <v>25.53333333333335</v>
+        <v>25.28419743333335</v>
       </c>
       <c r="O2">
-        <v>6.383333333333336</v>
+        <v>6.321049358333337</v>
       </c>
       <c r="P2">
-        <v>19.15000000000001</v>
+        <v>18.96314807500001</v>
       </c>
       <c r="Q2">
-        <v>73.95</v>
+        <v>73.763148075</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.083202787159014</v>
+        <v>0.08348614160718834</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381923</v>
+        <v>0.5829926250339362</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>102.4875713750341</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08302853019111646</v>
+        <v>0.08285427322321894</v>
       </c>
       <c r="C3">
-        <v>452.0377034760818</v>
+        <v>449.0306575337299</v>
       </c>
       <c r="D3">
-        <v>413.7907034760818</v>
+        <v>415.73665753373</v>
       </c>
       <c r="E3">
-        <v>-367.447</v>
+        <v>-362.494</v>
       </c>
       <c r="F3">
-        <v>4.952999999999999</v>
+        <v>9.905999999999999</v>
       </c>
       <c r="G3">
         <v>43.2</v>
@@ -1533,28 +1533,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M3">
-        <v>0.2491359</v>
+        <v>0.4982717999999999</v>
       </c>
       <c r="N3">
-        <v>25.28419743333335</v>
+        <v>25.03506153333334</v>
       </c>
       <c r="O3">
-        <v>6.321049358333337</v>
+        <v>6.258765383333336</v>
       </c>
       <c r="P3">
-        <v>18.96314807500001</v>
+        <v>18.77629615000001</v>
       </c>
       <c r="Q3">
-        <v>73.763148075</v>
+        <v>73.57629615</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08348614160718834</v>
+        <v>0.08377527879920299</v>
       </c>
       <c r="T3">
-        <v>0.5829926250339362</v>
+        <v>0.5874654854377566</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>102.4875713750341</v>
+        <v>51.24378568751703</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08285427322321894</v>
+        <v>0.08268001625532138</v>
       </c>
       <c r="C4">
-        <v>449.0306575337299</v>
+        <v>446.0420007402012</v>
       </c>
       <c r="D4">
-        <v>415.73665753373</v>
+        <v>417.7010007402012</v>
       </c>
       <c r="E4">
-        <v>-362.494</v>
+        <v>-357.541</v>
       </c>
       <c r="F4">
-        <v>9.905999999999999</v>
+        <v>14.859</v>
       </c>
       <c r="G4">
         <v>43.2</v>
@@ -1615,28 +1615,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M4">
-        <v>0.4982717999999999</v>
+        <v>0.7474076999999999</v>
       </c>
       <c r="N4">
-        <v>25.03506153333334</v>
+        <v>24.78592563333335</v>
       </c>
       <c r="O4">
-        <v>6.258765383333336</v>
+        <v>6.196481408333336</v>
       </c>
       <c r="P4">
-        <v>18.77629615000001</v>
+        <v>18.58944422500001</v>
       </c>
       <c r="Q4">
-        <v>73.57629615</v>
+        <v>73.38944422500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08377527879920299</v>
+        <v>0.08407037758280556</v>
       </c>
       <c r="T4">
-        <v>0.5874654854377566</v>
+        <v>0.5920305697674286</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.24378568751703</v>
+        <v>34.16252379167802</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08268001625532138</v>
+        <v>0.08250575928742385</v>
       </c>
       <c r="C5">
-        <v>446.0420007402012</v>
+        <v>443.0719949975</v>
       </c>
       <c r="D5">
-        <v>417.7010007402012</v>
+        <v>419.6839949975</v>
       </c>
       <c r="E5">
-        <v>-357.541</v>
+        <v>-352.588</v>
       </c>
       <c r="F5">
-        <v>14.859</v>
+        <v>19.812</v>
       </c>
       <c r="G5">
         <v>43.2</v>
@@ -1697,28 +1697,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M5">
-        <v>0.7474076999999999</v>
+        <v>0.9965435999999999</v>
       </c>
       <c r="N5">
-        <v>24.78592563333335</v>
+        <v>24.53678973333335</v>
       </c>
       <c r="O5">
-        <v>6.196481408333336</v>
+        <v>6.134197433333337</v>
       </c>
       <c r="P5">
-        <v>18.58944422500001</v>
+        <v>18.40259230000001</v>
       </c>
       <c r="Q5">
-        <v>73.38944422500001</v>
+        <v>73.20259230000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08407037758280556</v>
+        <v>0.08437162425773317</v>
       </c>
       <c r="T5">
-        <v>0.5920305697674286</v>
+        <v>0.5966907600206358</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.16252379167802</v>
+        <v>25.62189284375852</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08250575928742385</v>
+        <v>0.08233150231952632</v>
       </c>
       <c r="C6">
-        <v>443.0719949975</v>
+        <v>440.1209072047704</v>
       </c>
       <c r="D6">
-        <v>419.6839949975</v>
+        <v>421.6859072047704</v>
       </c>
       <c r="E6">
-        <v>-352.588</v>
+        <v>-347.635</v>
       </c>
       <c r="F6">
-        <v>19.812</v>
+        <v>24.765</v>
       </c>
       <c r="G6">
         <v>43.2</v>
@@ -1779,28 +1779,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M6">
-        <v>0.9965435999999999</v>
+        <v>1.2456795</v>
       </c>
       <c r="N6">
-        <v>24.53678973333335</v>
+        <v>24.28765383333334</v>
       </c>
       <c r="O6">
-        <v>6.134197433333337</v>
+        <v>6.071913458333336</v>
       </c>
       <c r="P6">
-        <v>18.40259230000001</v>
+        <v>18.21574037500001</v>
       </c>
       <c r="Q6">
-        <v>73.20259230000001</v>
+        <v>73.01574037500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08437162425773317</v>
+        <v>0.08467921296792244</v>
       </c>
       <c r="T6">
-        <v>0.5966907600206358</v>
+        <v>0.6014490595423315</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.62189284375852</v>
+        <v>20.49751427500681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08233150231952632</v>
+        <v>0.08215724535162879</v>
       </c>
       <c r="C7">
-        <v>440.1209072047704</v>
+        <v>437.1890093780497</v>
       </c>
       <c r="D7">
-        <v>421.6859072047704</v>
+        <v>423.7070093780497</v>
       </c>
       <c r="E7">
-        <v>-347.635</v>
+        <v>-342.682</v>
       </c>
       <c r="F7">
-        <v>24.765</v>
+        <v>29.718</v>
       </c>
       <c r="G7">
         <v>43.2</v>
@@ -1861,28 +1861,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M7">
-        <v>1.2456795</v>
+        <v>1.4948154</v>
       </c>
       <c r="N7">
-        <v>24.28765383333334</v>
+        <v>24.03851793333335</v>
       </c>
       <c r="O7">
-        <v>6.071913458333336</v>
+        <v>6.009629483333336</v>
       </c>
       <c r="P7">
-        <v>18.21574037500001</v>
+        <v>18.02888845000001</v>
       </c>
       <c r="Q7">
-        <v>73.01574037500001</v>
+        <v>72.82888845000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08467921296792244</v>
+        <v>0.08499334611875403</v>
       </c>
       <c r="T7">
-        <v>0.6014490595423315</v>
+        <v>0.6063085994793823</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.49751427500681</v>
+        <v>17.08126189583901</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08215724535162879</v>
+        <v>0.08198298838373125</v>
       </c>
       <c r="C8">
-        <v>437.1890093780497</v>
+        <v>434.2765787734828</v>
       </c>
       <c r="D8">
-        <v>423.7070093780497</v>
+        <v>425.7475787734828</v>
       </c>
       <c r="E8">
-        <v>-342.682</v>
+        <v>-337.729</v>
       </c>
       <c r="F8">
-        <v>29.718</v>
+        <v>34.67099999999999</v>
       </c>
       <c r="G8">
         <v>43.2</v>
@@ -1943,28 +1943,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M8">
-        <v>1.4948154</v>
+        <v>1.7439513</v>
       </c>
       <c r="N8">
-        <v>24.03851793333335</v>
+        <v>23.78938203333335</v>
       </c>
       <c r="O8">
-        <v>6.009629483333336</v>
+        <v>5.947345508333337</v>
       </c>
       <c r="P8">
-        <v>18.02888845000001</v>
+        <v>17.84203652500001</v>
       </c>
       <c r="Q8">
-        <v>72.82888845000001</v>
+        <v>72.64203652500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08499334611875403</v>
+        <v>0.08531423482121639</v>
       </c>
       <c r="T8">
-        <v>0.6063085994793823</v>
+        <v>0.6112726456516386</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.08126189583901</v>
+        <v>14.64108162500487</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08198298838373123</v>
+        <v>0.08189873141583372</v>
       </c>
       <c r="C9">
-        <v>434.2765787734829</v>
+        <v>430.3173034466283</v>
       </c>
       <c r="D9">
-        <v>425.7475787734829</v>
+        <v>426.7413034466283</v>
       </c>
       <c r="E9">
-        <v>-337.729</v>
+        <v>-332.776</v>
       </c>
       <c r="F9">
-        <v>34.671</v>
+        <v>39.624</v>
       </c>
       <c r="G9">
         <v>43.2</v>
@@ -2025,45 +2025,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M9">
-        <v>1.7439513</v>
+        <v>2.0525232</v>
       </c>
       <c r="N9">
-        <v>23.78938203333335</v>
+        <v>23.48081013333335</v>
       </c>
       <c r="O9">
-        <v>5.947345508333337</v>
+        <v>5.870202533333337</v>
       </c>
       <c r="P9">
-        <v>17.84203652500001</v>
+        <v>17.61060760000001</v>
       </c>
       <c r="Q9">
-        <v>72.64203652500001</v>
+        <v>72.41060760000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08531423482121639</v>
+        <v>0.08564209936503665</v>
       </c>
       <c r="T9">
-        <v>0.6112726456516386</v>
+        <v>0.6163446058711179</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.64108162500487</v>
+        <v>12.43997306989434</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08189873141583372</v>
+        <v>0.08173572444793618</v>
       </c>
       <c r="C10">
-        <v>430.3173034466283</v>
+        <v>427.3000319457784</v>
       </c>
       <c r="D10">
-        <v>426.7413034466283</v>
+        <v>428.6770319457784</v>
       </c>
       <c r="E10">
-        <v>-332.776</v>
+        <v>-327.823</v>
       </c>
       <c r="F10">
-        <v>39.624</v>
+        <v>44.57699999999999</v>
       </c>
       <c r="G10">
         <v>43.2</v>
@@ -2107,28 +2107,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M10">
-        <v>2.0525232</v>
+        <v>2.309088599999999</v>
       </c>
       <c r="N10">
-        <v>23.48081013333335</v>
+        <v>23.22424473333335</v>
       </c>
       <c r="O10">
-        <v>5.870202533333337</v>
+        <v>5.806061183333337</v>
       </c>
       <c r="P10">
-        <v>17.61060760000001</v>
+        <v>17.41818355000001</v>
       </c>
       <c r="Q10">
-        <v>72.41060760000001</v>
+        <v>72.21818355000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08564209936503665</v>
+        <v>0.08597716972300679</v>
       </c>
       <c r="T10">
-        <v>0.6163446058711179</v>
+        <v>0.6215280377437725</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.43997306989434</v>
+        <v>11.05775383990608</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08173572444793618</v>
+        <v>0.08157271748003865</v>
       </c>
       <c r="C11">
-        <v>427.3000319457784</v>
+        <v>424.3004016673767</v>
       </c>
       <c r="D11">
-        <v>428.6770319457784</v>
+        <v>430.6304016673767</v>
       </c>
       <c r="E11">
-        <v>-327.823</v>
+        <v>-322.87</v>
       </c>
       <c r="F11">
-        <v>44.57699999999999</v>
+        <v>49.52999999999999</v>
       </c>
       <c r="G11">
         <v>43.2</v>
@@ -2189,28 +2189,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M11">
-        <v>2.309088599999999</v>
+        <v>2.565653999999999</v>
       </c>
       <c r="N11">
-        <v>23.22424473333335</v>
+        <v>22.96767933333335</v>
       </c>
       <c r="O11">
-        <v>5.806061183333337</v>
+        <v>5.741919833333337</v>
       </c>
       <c r="P11">
-        <v>17.41818355000001</v>
+        <v>17.22575950000001</v>
       </c>
       <c r="Q11">
-        <v>72.21818355000001</v>
+        <v>72.02575950000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08597716972300679</v>
+        <v>0.08631968608893183</v>
       </c>
       <c r="T11">
-        <v>0.6215280377437725</v>
+        <v>0.626826656991375</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.05775383990608</v>
+        <v>9.951978455915471</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08157271748003865</v>
+        <v>0.08154996051214111</v>
       </c>
       <c r="C12">
-        <v>424.3004016673767</v>
+        <v>419.6215234310391</v>
       </c>
       <c r="D12">
-        <v>430.6304016673767</v>
+        <v>430.9045234310391</v>
       </c>
       <c r="E12">
-        <v>-322.87</v>
+        <v>-317.917</v>
       </c>
       <c r="F12">
-        <v>49.53</v>
+        <v>54.483</v>
       </c>
       <c r="G12">
         <v>43.2</v>
@@ -2271,45 +2271,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M12">
-        <v>2.565654</v>
+        <v>2.9148405</v>
       </c>
       <c r="N12">
-        <v>22.96767933333335</v>
+        <v>22.61849283333335</v>
       </c>
       <c r="O12">
-        <v>5.741919833333337</v>
+        <v>5.654623208333336</v>
       </c>
       <c r="P12">
-        <v>17.22575950000001</v>
+        <v>16.96386962500001</v>
       </c>
       <c r="Q12">
-        <v>72.02575950000001</v>
+        <v>71.76386962500001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08631968608893183</v>
+        <v>0.08666989945184395</v>
       </c>
       <c r="T12">
-        <v>0.626826656991375</v>
+        <v>0.6322443463344293</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>9.951978455915469</v>
+        <v>8.759770331629928</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08154996051214111</v>
+        <v>0.08139970354424358</v>
       </c>
       <c r="C13">
-        <v>419.6215234310391</v>
+        <v>416.4872578781844</v>
       </c>
       <c r="D13">
-        <v>430.9045234310391</v>
+        <v>432.7232578781844</v>
       </c>
       <c r="E13">
-        <v>-317.917</v>
+        <v>-312.964</v>
       </c>
       <c r="F13">
-        <v>54.483</v>
+        <v>59.43599999999999</v>
       </c>
       <c r="G13">
         <v>43.2</v>
@@ -2353,28 +2353,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M13">
-        <v>2.9148405</v>
+        <v>3.179825999999999</v>
       </c>
       <c r="N13">
-        <v>22.61849283333335</v>
+        <v>22.35350733333335</v>
       </c>
       <c r="O13">
-        <v>5.654623208333336</v>
+        <v>5.588376833333337</v>
       </c>
       <c r="P13">
-        <v>16.96386962500001</v>
+        <v>16.76513050000001</v>
       </c>
       <c r="Q13">
-        <v>71.76386962500001</v>
+        <v>71.56513050000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08666989945184395</v>
+        <v>0.0870280722093677</v>
       </c>
       <c r="T13">
-        <v>0.6322443463344293</v>
+        <v>0.6377851649807347</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.759770331629928</v>
+        <v>8.02978947066077</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08139970354424358</v>
+        <v>0.08132744657634604</v>
       </c>
       <c r="C14">
-        <v>416.4872578781844</v>
+        <v>412.4143456290964</v>
       </c>
       <c r="D14">
-        <v>432.7232578781844</v>
+        <v>433.6033456290965</v>
       </c>
       <c r="E14">
-        <v>-312.964</v>
+        <v>-308.011</v>
       </c>
       <c r="F14">
-        <v>59.43599999999999</v>
+        <v>64.389</v>
       </c>
       <c r="G14">
         <v>43.2</v>
@@ -2435,45 +2435,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M14">
-        <v>3.179825999999999</v>
+        <v>3.4963227</v>
       </c>
       <c r="N14">
-        <v>22.35350733333335</v>
+        <v>22.03701063333335</v>
       </c>
       <c r="O14">
-        <v>5.588376833333337</v>
+        <v>5.509252658333336</v>
       </c>
       <c r="P14">
-        <v>16.76513050000001</v>
+        <v>16.52775797500001</v>
       </c>
       <c r="Q14">
-        <v>71.56513050000001</v>
+        <v>71.327757975</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0870280722093677</v>
+        <v>0.08739447882338625</v>
       </c>
       <c r="T14">
-        <v>0.6377851649807347</v>
+        <v>0.6434533587683345</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.02978947066077</v>
+        <v>7.302910950792199</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08132744657634604</v>
+        <v>0.0811831896084485</v>
       </c>
       <c r="C15">
-        <v>412.4143456290964</v>
+        <v>409.2291428402259</v>
       </c>
       <c r="D15">
-        <v>433.6033456290965</v>
+        <v>435.3711428402259</v>
       </c>
       <c r="E15">
-        <v>-308.011</v>
+        <v>-303.058</v>
       </c>
       <c r="F15">
-        <v>64.389</v>
+        <v>69.342</v>
       </c>
       <c r="G15">
         <v>43.2</v>
@@ -2517,28 +2517,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M15">
-        <v>3.4963227</v>
+        <v>3.7652706</v>
       </c>
       <c r="N15">
-        <v>22.03701063333335</v>
+        <v>21.76806273333334</v>
       </c>
       <c r="O15">
-        <v>5.509252658333336</v>
+        <v>5.442015683333336</v>
       </c>
       <c r="P15">
-        <v>16.52775797500001</v>
+        <v>16.32604705000001</v>
       </c>
       <c r="Q15">
-        <v>71.327757975</v>
+        <v>71.12604705000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08739447882338625</v>
+        <v>0.08776940652145175</v>
       </c>
       <c r="T15">
-        <v>0.6434533587683345</v>
+        <v>0.6492533710161111</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.302910950792199</v>
+        <v>6.781274454307041</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0811831896084485</v>
+        <v>0.08103893264055095</v>
       </c>
       <c r="C16">
-        <v>409.2291428402259</v>
+        <v>406.0584136489606</v>
       </c>
       <c r="D16">
-        <v>435.3711428402259</v>
+        <v>437.1534136489606</v>
       </c>
       <c r="E16">
-        <v>-303.058</v>
+        <v>-298.105</v>
       </c>
       <c r="F16">
-        <v>69.342</v>
+        <v>74.295</v>
       </c>
       <c r="G16">
         <v>43.2</v>
@@ -2599,28 +2599,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M16">
-        <v>3.7652706</v>
+        <v>4.034218500000001</v>
       </c>
       <c r="N16">
-        <v>21.76806273333334</v>
+        <v>21.49911483333334</v>
       </c>
       <c r="O16">
-        <v>5.442015683333336</v>
+        <v>5.374778708333336</v>
       </c>
       <c r="P16">
-        <v>16.32604705000001</v>
+        <v>16.12433612500001</v>
       </c>
       <c r="Q16">
-        <v>71.12604705000001</v>
+        <v>70.924336125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08776940652145175</v>
+        <v>0.08815315604770702</v>
       </c>
       <c r="T16">
-        <v>0.6492533710161111</v>
+        <v>0.6551898541403059</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.781274454307041</v>
+        <v>6.329189490686571</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08103893264055095</v>
+        <v>0.08101467567265343</v>
       </c>
       <c r="C17">
-        <v>406.0584136489606</v>
+        <v>401.4065385668712</v>
       </c>
       <c r="D17">
-        <v>437.1534136489606</v>
+        <v>437.4545385668712</v>
       </c>
       <c r="E17">
-        <v>-298.105</v>
+        <v>-293.152</v>
       </c>
       <c r="F17">
-        <v>74.29499999999999</v>
+        <v>79.24799999999999</v>
       </c>
       <c r="G17">
         <v>43.2</v>
@@ -2681,45 +2681,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M17">
-        <v>4.0342185</v>
+        <v>4.3824144</v>
       </c>
       <c r="N17">
-        <v>21.49911483333334</v>
+        <v>21.15091893333334</v>
       </c>
       <c r="O17">
-        <v>5.374778708333336</v>
+        <v>5.287729733333336</v>
       </c>
       <c r="P17">
-        <v>16.12433612500001</v>
+        <v>15.86318920000001</v>
       </c>
       <c r="Q17">
-        <v>70.924336125</v>
+        <v>70.66318920000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08815315604770702</v>
+        <v>0.08854604246744456</v>
       </c>
       <c r="T17">
-        <v>0.6551898541403059</v>
+        <v>0.6612676821007911</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.329189490686572</v>
+        <v>5.826316501089751</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08101467567265343</v>
+        <v>0.0808779187047559</v>
       </c>
       <c r="C18">
-        <v>401.4065385668712</v>
+        <v>398.1590261926038</v>
       </c>
       <c r="D18">
-        <v>437.4545385668712</v>
+        <v>439.1600261926039</v>
       </c>
       <c r="E18">
-        <v>-293.152</v>
+        <v>-288.199</v>
       </c>
       <c r="F18">
-        <v>79.24799999999999</v>
+        <v>84.20099999999999</v>
       </c>
       <c r="G18">
         <v>43.2</v>
@@ -2763,28 +2763,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M18">
-        <v>4.3824144</v>
+        <v>4.6563153</v>
       </c>
       <c r="N18">
-        <v>21.15091893333334</v>
+        <v>20.87701803333335</v>
       </c>
       <c r="O18">
-        <v>5.287729733333336</v>
+        <v>5.219254508333337</v>
       </c>
       <c r="P18">
-        <v>15.86318920000001</v>
+        <v>15.65776352500001</v>
       </c>
       <c r="Q18">
-        <v>70.66318920000001</v>
+        <v>70.457763525</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08854604246744456</v>
+        <v>0.08894839602982639</v>
       </c>
       <c r="T18">
-        <v>0.6612676821007911</v>
+        <v>0.6674919637470713</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.826316501089751</v>
+        <v>5.483592001025649</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0808779187047559</v>
+        <v>0.08074116173685836</v>
       </c>
       <c r="C19">
-        <v>398.1590261926038</v>
+        <v>394.9248641080745</v>
       </c>
       <c r="D19">
-        <v>439.1600261926039</v>
+        <v>440.8788641080745</v>
       </c>
       <c r="E19">
-        <v>-288.199</v>
+        <v>-283.246</v>
       </c>
       <c r="F19">
-        <v>84.20099999999999</v>
+        <v>89.154</v>
       </c>
       <c r="G19">
         <v>43.2</v>
@@ -2845,28 +2845,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M19">
-        <v>4.6563153</v>
+        <v>4.9302162</v>
       </c>
       <c r="N19">
-        <v>20.87701803333335</v>
+        <v>20.60311713333335</v>
       </c>
       <c r="O19">
-        <v>5.219254508333337</v>
+        <v>5.150779283333336</v>
       </c>
       <c r="P19">
-        <v>15.65776352500001</v>
+        <v>15.45233785000001</v>
       </c>
       <c r="Q19">
-        <v>70.457763525</v>
+        <v>70.25233785</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08894839602982639</v>
+        <v>0.08936056309372971</v>
       </c>
       <c r="T19">
-        <v>0.6674919637470713</v>
+        <v>0.6738680571408214</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.483592001025649</v>
+        <v>5.178948000968668</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08074116173685837</v>
+        <v>0.08060440476896084</v>
       </c>
       <c r="C20">
-        <v>394.9248641080744</v>
+        <v>391.7042096851865</v>
       </c>
       <c r="D20">
-        <v>440.8788641080744</v>
+        <v>442.6112096851865</v>
       </c>
       <c r="E20">
-        <v>-283.246</v>
+        <v>-278.293</v>
       </c>
       <c r="F20">
-        <v>89.15399999999998</v>
+        <v>94.107</v>
       </c>
       <c r="G20">
         <v>43.2</v>
@@ -2927,28 +2927,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M20">
-        <v>4.930216199999999</v>
+        <v>5.2041171</v>
       </c>
       <c r="N20">
-        <v>20.60311713333335</v>
+        <v>20.32921623333334</v>
       </c>
       <c r="O20">
-        <v>5.150779283333336</v>
+        <v>5.082304058333336</v>
       </c>
       <c r="P20">
-        <v>15.45233785000001</v>
+        <v>15.24691217500001</v>
       </c>
       <c r="Q20">
-        <v>70.25233785</v>
+        <v>70.046912175</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08936056309372971</v>
+        <v>0.08978290712217388</v>
       </c>
       <c r="T20">
-        <v>0.6738680571408214</v>
+        <v>0.6804015849393559</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.178948000968669</v>
+        <v>4.90637179039137</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08060440476896084</v>
+        <v>0.08046764780106329</v>
       </c>
       <c r="C21">
-        <v>391.7042096851865</v>
+        <v>388.4972227790473</v>
       </c>
       <c r="D21">
-        <v>442.6112096851865</v>
+        <v>444.3572227790473</v>
       </c>
       <c r="E21">
-        <v>-278.293</v>
+        <v>-273.34</v>
       </c>
       <c r="F21">
-        <v>94.107</v>
+        <v>99.06</v>
       </c>
       <c r="G21">
         <v>43.2</v>
@@ -3009,28 +3009,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M21">
-        <v>5.2041171</v>
+        <v>5.478018</v>
       </c>
       <c r="N21">
-        <v>20.32921623333334</v>
+        <v>20.05531533333335</v>
       </c>
       <c r="O21">
-        <v>5.082304058333336</v>
+        <v>5.013828833333337</v>
       </c>
       <c r="P21">
-        <v>15.24691217500001</v>
+        <v>15.04148650000001</v>
       </c>
       <c r="Q21">
-        <v>70.046912175</v>
+        <v>69.8414865</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08978290712217388</v>
+        <v>0.09021580975132912</v>
       </c>
       <c r="T21">
-        <v>0.6804015849393559</v>
+        <v>0.6870984509328534</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.90637179039137</v>
+        <v>4.661053200871802</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08046764780106329</v>
+        <v>0.08072464083316576</v>
       </c>
       <c r="C22">
-        <v>388.4972227790473</v>
+        <v>380.2744193596182</v>
       </c>
       <c r="D22">
-        <v>444.3572227790473</v>
+        <v>441.0874193596182</v>
       </c>
       <c r="E22">
-        <v>-273.34</v>
+        <v>-268.3869999999999</v>
       </c>
       <c r="F22">
-        <v>99.06</v>
+        <v>104.013</v>
       </c>
       <c r="G22">
         <v>43.2</v>
@@ -3091,45 +3091,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M22">
-        <v>5.478018</v>
+        <v>6.011951400000001</v>
       </c>
       <c r="N22">
-        <v>20.05531533333335</v>
+        <v>19.52138193333334</v>
       </c>
       <c r="O22">
-        <v>5.013828833333337</v>
+        <v>4.880345483333336</v>
       </c>
       <c r="P22">
-        <v>15.04148650000001</v>
+        <v>14.64103645000001</v>
       </c>
       <c r="Q22">
-        <v>69.8414865</v>
+        <v>69.44103645000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09021580975132912</v>
+        <v>0.09065967194071614</v>
       </c>
       <c r="T22">
-        <v>0.6870984509328534</v>
+        <v>0.6939648578375787</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.661053200871802</v>
+        <v>4.247095765500257</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08072464083316576</v>
+        <v>0.08060663386526823</v>
       </c>
       <c r="C23">
-        <v>380.2744193596182</v>
+        <v>376.8168638526955</v>
       </c>
       <c r="D23">
-        <v>441.0874193596182</v>
+        <v>442.5828638526955</v>
       </c>
       <c r="E23">
-        <v>-268.387</v>
+        <v>-263.434</v>
       </c>
       <c r="F23">
-        <v>104.013</v>
+        <v>108.966</v>
       </c>
       <c r="G23">
         <v>43.2</v>
@@ -3173,28 +3173,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M23">
-        <v>6.0119514</v>
+        <v>6.2982348</v>
       </c>
       <c r="N23">
-        <v>19.52138193333334</v>
+        <v>19.23509853333335</v>
       </c>
       <c r="O23">
-        <v>4.880345483333336</v>
+        <v>4.808774633333337</v>
       </c>
       <c r="P23">
-        <v>14.64103645000001</v>
+        <v>14.42632390000001</v>
       </c>
       <c r="Q23">
-        <v>69.44103645000001</v>
+        <v>69.22632390000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09065967194071614</v>
+        <v>0.09111491521188234</v>
       </c>
       <c r="T23">
-        <v>0.6939648578375787</v>
+        <v>0.7010073264578098</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.247095765500257</v>
+        <v>4.054045957977518</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08060663386526823</v>
+        <v>0.0810923768973707</v>
       </c>
       <c r="C24">
-        <v>376.8168638526955</v>
+        <v>365.7724197181856</v>
       </c>
       <c r="D24">
-        <v>442.5828638526955</v>
+        <v>436.4914197181856</v>
       </c>
       <c r="E24">
-        <v>-263.434</v>
+        <v>-258.481</v>
       </c>
       <c r="F24">
-        <v>108.966</v>
+        <v>113.919</v>
       </c>
       <c r="G24">
         <v>43.2</v>
@@ -3255,45 +3255,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M24">
-        <v>6.2982348</v>
+        <v>6.9832347</v>
       </c>
       <c r="N24">
-        <v>19.23509853333335</v>
+        <v>18.55009863333335</v>
       </c>
       <c r="O24">
-        <v>4.808774633333337</v>
+        <v>4.637524658333336</v>
       </c>
       <c r="P24">
-        <v>14.42632390000001</v>
+        <v>13.91257397500001</v>
       </c>
       <c r="Q24">
-        <v>69.22632390000001</v>
+        <v>68.712573975</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09111491521188234</v>
+        <v>0.09158198298359829</v>
       </c>
       <c r="T24">
-        <v>0.7010073264578098</v>
+        <v>0.7082327163409042</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.054045957977518</v>
+        <v>3.656376225380674</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0810923768973707</v>
+        <v>0.08100061992947316</v>
       </c>
       <c r="C25">
-        <v>365.7724197181856</v>
+        <v>361.9572158498128</v>
       </c>
       <c r="D25">
-        <v>436.4914197181856</v>
+        <v>437.6292158498128</v>
       </c>
       <c r="E25">
-        <v>-258.481</v>
+        <v>-253.528</v>
       </c>
       <c r="F25">
-        <v>113.919</v>
+        <v>118.872</v>
       </c>
       <c r="G25">
         <v>43.2</v>
@@ -3337,28 +3337,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M25">
-        <v>6.9832347</v>
+        <v>7.2868536</v>
       </c>
       <c r="N25">
-        <v>18.55009863333335</v>
+        <v>18.24647973333335</v>
       </c>
       <c r="O25">
-        <v>4.637524658333336</v>
+        <v>4.561619933333336</v>
       </c>
       <c r="P25">
-        <v>13.91257397500001</v>
+        <v>13.68485980000001</v>
       </c>
       <c r="Q25">
-        <v>68.712573975</v>
+        <v>68.48485980000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09158198298359829</v>
+        <v>0.09206134201246469</v>
       </c>
       <c r="T25">
-        <v>0.7082327163409042</v>
+        <v>0.7156482480630274</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.656376225380674</v>
+        <v>3.504027215989813</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08100061992947316</v>
+        <v>0.08143386296157562</v>
       </c>
       <c r="C26">
-        <v>361.9572158498128</v>
+        <v>351.6834396932719</v>
       </c>
       <c r="D26">
-        <v>437.6292158498128</v>
+        <v>432.3084396932719</v>
       </c>
       <c r="E26">
-        <v>-253.528</v>
+        <v>-248.575</v>
       </c>
       <c r="F26">
-        <v>118.872</v>
+        <v>123.825</v>
       </c>
       <c r="G26">
         <v>43.2</v>
@@ -3419,45 +3419,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M26">
-        <v>7.286853599999999</v>
+        <v>7.9371825</v>
       </c>
       <c r="N26">
-        <v>18.24647973333335</v>
+        <v>17.59615083333335</v>
       </c>
       <c r="O26">
-        <v>4.561619933333336</v>
+        <v>4.399037708333337</v>
       </c>
       <c r="P26">
-        <v>13.68485980000001</v>
+        <v>13.19711312500001</v>
       </c>
       <c r="Q26">
-        <v>68.48485980000001</v>
+        <v>67.99711312500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09206134201246469</v>
+        <v>0.0925534839487675</v>
       </c>
       <c r="T26">
-        <v>0.7156482480630274</v>
+        <v>0.7232615272977404</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.504027215989813</v>
+        <v>3.216926577325562</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08143386296157562</v>
+        <v>0.08136310599367808</v>
       </c>
       <c r="C27">
-        <v>351.6834396932719</v>
+        <v>347.5905680069983</v>
       </c>
       <c r="D27">
-        <v>432.3084396932719</v>
+        <v>433.1685680069983</v>
       </c>
       <c r="E27">
-        <v>-248.575</v>
+        <v>-243.622</v>
       </c>
       <c r="F27">
-        <v>123.825</v>
+        <v>128.778</v>
       </c>
       <c r="G27">
         <v>43.2</v>
@@ -3501,28 +3501,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M27">
-        <v>7.9371825</v>
+        <v>8.2546698</v>
       </c>
       <c r="N27">
-        <v>17.59615083333335</v>
+        <v>17.27866353333334</v>
       </c>
       <c r="O27">
-        <v>4.399037708333337</v>
+        <v>4.319665883333336</v>
       </c>
       <c r="P27">
-        <v>13.19711312500001</v>
+        <v>12.95899765000001</v>
       </c>
       <c r="Q27">
-        <v>67.99711312500001</v>
+        <v>67.75899765</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0925534839487675</v>
+        <v>0.09305892701848389</v>
       </c>
       <c r="T27">
-        <v>0.7232615272977404</v>
+        <v>0.7310805708360943</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.216926577325562</v>
+        <v>3.093198632043809</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08136310599367808</v>
+        <v>0.08287184902578056</v>
       </c>
       <c r="C28">
-        <v>347.5905680069983</v>
+        <v>325.0085563477233</v>
       </c>
       <c r="D28">
-        <v>433.1685680069983</v>
+        <v>415.5395563477233</v>
       </c>
       <c r="E28">
-        <v>-243.622</v>
+        <v>-238.669</v>
       </c>
       <c r="F28">
-        <v>128.778</v>
+        <v>133.731</v>
       </c>
       <c r="G28">
         <v>43.2</v>
@@ -3583,45 +3583,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M28">
-        <v>8.2546698</v>
+        <v>9.615258900000001</v>
       </c>
       <c r="N28">
-        <v>17.27866353333334</v>
+        <v>15.91807443333335</v>
       </c>
       <c r="O28">
-        <v>4.319665883333336</v>
+        <v>3.979518608333336</v>
       </c>
       <c r="P28">
-        <v>12.95899765000001</v>
+        <v>11.93855582500001</v>
       </c>
       <c r="Q28">
-        <v>67.75899765</v>
+        <v>66.73855582500001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09305892701848389</v>
+        <v>0.09357821784353501</v>
       </c>
       <c r="T28">
-        <v>0.7310805708360943</v>
+        <v>0.7391138347453622</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.093198632043809</v>
+        <v>2.655501385753986</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08287184902578056</v>
+        <v>0.08285959205788303</v>
       </c>
       <c r="C29">
-        <v>325.0085563477233</v>
+        <v>320.1929905373482</v>
       </c>
       <c r="D29">
-        <v>415.5395563477233</v>
+        <v>415.6769905373483</v>
       </c>
       <c r="E29">
-        <v>-238.669</v>
+        <v>-233.716</v>
       </c>
       <c r="F29">
-        <v>133.731</v>
+        <v>138.684</v>
       </c>
       <c r="G29">
         <v>43.2</v>
@@ -3665,28 +3665,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M29">
-        <v>9.615258900000001</v>
+        <v>9.971379600000001</v>
       </c>
       <c r="N29">
-        <v>15.91807443333335</v>
+        <v>15.56195373333335</v>
       </c>
       <c r="O29">
-        <v>3.979518608333336</v>
+        <v>3.890488433333336</v>
       </c>
       <c r="P29">
-        <v>11.93855582500001</v>
+        <v>11.67146530000001</v>
       </c>
       <c r="Q29">
-        <v>66.73855582500001</v>
+        <v>66.47146530000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09357821784353501</v>
+        <v>0.09411193341372642</v>
       </c>
       <c r="T29">
-        <v>0.7391138347453622</v>
+        <v>0.7473702448743318</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.655501385753986</v>
+        <v>2.560662050548486</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08285959205788303</v>
+        <v>0.08369558508998548</v>
       </c>
       <c r="C30">
-        <v>320.1929905373482</v>
+        <v>306.0699759599411</v>
       </c>
       <c r="D30">
-        <v>415.6769905373483</v>
+        <v>406.5069759599411</v>
       </c>
       <c r="E30">
-        <v>-233.716</v>
+        <v>-228.763</v>
       </c>
       <c r="F30">
-        <v>138.684</v>
+        <v>143.637</v>
       </c>
       <c r="G30">
         <v>43.2</v>
@@ -3747,45 +3747,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M30">
-        <v>9.971379600000001</v>
+        <v>10.8876846</v>
       </c>
       <c r="N30">
-        <v>15.56195373333335</v>
+        <v>14.64564873333335</v>
       </c>
       <c r="O30">
-        <v>3.890488433333336</v>
+        <v>3.661412183333336</v>
       </c>
       <c r="P30">
-        <v>11.67146530000001</v>
+        <v>10.98423655000001</v>
       </c>
       <c r="Q30">
-        <v>66.47146530000001</v>
+        <v>65.78423655</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09411193341372642</v>
+        <v>0.09466068322533167</v>
       </c>
       <c r="T30">
-        <v>0.7473702448743318</v>
+        <v>0.7558592299365118</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.560662050548486</v>
+        <v>2.345157328798204</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08369558508998548</v>
+        <v>0.08371257812208793</v>
       </c>
       <c r="C31">
-        <v>306.0699759599411</v>
+        <v>300.9347729435671</v>
       </c>
       <c r="D31">
-        <v>406.5069759599411</v>
+        <v>406.3247729435671</v>
       </c>
       <c r="E31">
-        <v>-228.763</v>
+        <v>-223.81</v>
       </c>
       <c r="F31">
-        <v>143.637</v>
+        <v>148.59</v>
       </c>
       <c r="G31">
         <v>43.2</v>
@@ -3829,28 +3829,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M31">
-        <v>10.8876846</v>
+        <v>11.263122</v>
       </c>
       <c r="N31">
-        <v>14.64564873333335</v>
+        <v>14.27021133333335</v>
       </c>
       <c r="O31">
-        <v>3.661412183333337</v>
+        <v>3.567552833333337</v>
       </c>
       <c r="P31">
-        <v>10.98423655000001</v>
+        <v>10.70265850000001</v>
       </c>
       <c r="Q31">
-        <v>65.78423655</v>
+        <v>65.50265850000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09466068322533167</v>
+        <v>0.09522511160298278</v>
       </c>
       <c r="T31">
-        <v>0.7558592299365118</v>
+        <v>0.7645907574290398</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.345157328798205</v>
+        <v>2.266985417838264</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08371257812208793</v>
+        <v>0.0837295711541904</v>
       </c>
       <c r="C32">
-        <v>300.9347729435671</v>
+        <v>295.7997331867086</v>
       </c>
       <c r="D32">
-        <v>406.3247729435671</v>
+        <v>406.1427331867086</v>
       </c>
       <c r="E32">
-        <v>-223.81</v>
+        <v>-218.857</v>
       </c>
       <c r="F32">
-        <v>148.59</v>
+        <v>153.543</v>
       </c>
       <c r="G32">
         <v>43.2</v>
@@ -3911,28 +3911,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M32">
-        <v>11.263122</v>
+        <v>11.6385594</v>
       </c>
       <c r="N32">
-        <v>14.27021133333335</v>
+        <v>13.89477393333335</v>
       </c>
       <c r="O32">
-        <v>3.567552833333337</v>
+        <v>3.473693483333336</v>
       </c>
       <c r="P32">
-        <v>10.70265850000001</v>
+        <v>10.42108045000001</v>
       </c>
       <c r="Q32">
-        <v>65.50265850000001</v>
+        <v>65.22108045</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09522511160298278</v>
+        <v>0.09580590022346436</v>
       </c>
       <c r="T32">
-        <v>0.7645907574290398</v>
+        <v>0.7735753726749744</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.266985417838264</v>
+        <v>2.193856855972514</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0837295711541904</v>
+        <v>0.08374656418629288</v>
       </c>
       <c r="C33">
-        <v>295.7997331867086</v>
+        <v>290.6648564700354</v>
       </c>
       <c r="D33">
-        <v>406.1427331867086</v>
+        <v>405.9608564700354</v>
       </c>
       <c r="E33">
-        <v>-218.857</v>
+        <v>-213.904</v>
       </c>
       <c r="F33">
-        <v>153.543</v>
+        <v>158.496</v>
       </c>
       <c r="G33">
         <v>43.2</v>
@@ -3993,28 +3993,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M33">
-        <v>11.6385594</v>
+        <v>12.0139968</v>
       </c>
       <c r="N33">
-        <v>13.89477393333335</v>
+        <v>13.51933653333335</v>
       </c>
       <c r="O33">
-        <v>3.473693483333336</v>
+        <v>3.379834133333337</v>
       </c>
       <c r="P33">
-        <v>10.42108045000001</v>
+        <v>10.13950240000001</v>
       </c>
       <c r="Q33">
-        <v>65.22108045</v>
+        <v>64.93950240000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09580590022346436</v>
+        <v>0.09640377086219541</v>
       </c>
       <c r="T33">
-        <v>0.7735753726749744</v>
+        <v>0.7828242413104955</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.193856855972514</v>
+        <v>2.125298829223373</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08374656418629288</v>
+        <v>0.08376355721839533</v>
       </c>
       <c r="C34">
-        <v>290.6648564700354</v>
+        <v>285.5301425746106</v>
       </c>
       <c r="D34">
-        <v>405.9608564700354</v>
+        <v>405.7791425746107</v>
       </c>
       <c r="E34">
-        <v>-213.904</v>
+        <v>-208.951</v>
       </c>
       <c r="F34">
-        <v>158.496</v>
+        <v>163.449</v>
       </c>
       <c r="G34">
         <v>43.2</v>
@@ -4075,28 +4075,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M34">
-        <v>12.0139968</v>
+        <v>12.3894342</v>
       </c>
       <c r="N34">
-        <v>13.51933653333335</v>
+        <v>13.14389913333335</v>
       </c>
       <c r="O34">
-        <v>3.379834133333337</v>
+        <v>3.285974783333336</v>
       </c>
       <c r="P34">
-        <v>10.13950240000001</v>
+        <v>9.857924350000008</v>
       </c>
       <c r="Q34">
-        <v>64.93950240000001</v>
+        <v>64.65792435</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09640377086219541</v>
+        <v>0.0970194883856647</v>
       </c>
       <c r="T34">
-        <v>0.7828242413104955</v>
+        <v>0.7923491955769276</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.125298829223373</v>
+        <v>2.060895834398422</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08376355721839533</v>
+        <v>0.08378055025049781</v>
       </c>
       <c r="C35">
-        <v>285.5301425746106</v>
+        <v>280.3955912818883</v>
       </c>
       <c r="D35">
-        <v>405.7791425746107</v>
+        <v>405.5975912818883</v>
       </c>
       <c r="E35">
-        <v>-208.951</v>
+        <v>-203.998</v>
       </c>
       <c r="F35">
-        <v>163.449</v>
+        <v>168.402</v>
       </c>
       <c r="G35">
         <v>43.2</v>
@@ -4157,28 +4157,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M35">
-        <v>12.3894342</v>
+        <v>12.7648716</v>
       </c>
       <c r="N35">
-        <v>13.14389913333335</v>
+        <v>12.76846173333335</v>
       </c>
       <c r="O35">
-        <v>3.285974783333336</v>
+        <v>3.192115433333337</v>
       </c>
       <c r="P35">
-        <v>9.857924350000008</v>
+        <v>9.57634630000001</v>
       </c>
       <c r="Q35">
-        <v>64.65792435</v>
+        <v>64.37634630000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0970194883856647</v>
+        <v>0.09765386401590578</v>
       </c>
       <c r="T35">
-        <v>0.7923491955769276</v>
+        <v>0.8021627848211303</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.060895834398422</v>
+        <v>2.000281251033763</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08378055025049781</v>
+        <v>0.08752504328260027</v>
       </c>
       <c r="C36">
-        <v>280.3955912818883</v>
+        <v>239.0434114390741</v>
       </c>
       <c r="D36">
-        <v>405.5975912818883</v>
+        <v>369.1984114390741</v>
       </c>
       <c r="E36">
-        <v>-203.998</v>
+        <v>-199.045</v>
       </c>
       <c r="F36">
-        <v>168.402</v>
+        <v>173.355</v>
       </c>
       <c r="G36">
         <v>43.2</v>
@@ -4239,45 +4239,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M36">
-        <v>12.7648716</v>
+        <v>15.60195</v>
       </c>
       <c r="N36">
-        <v>12.76846173333335</v>
+        <v>9.931383333333347</v>
       </c>
       <c r="O36">
-        <v>3.192115433333337</v>
+        <v>2.482845833333337</v>
       </c>
       <c r="P36">
-        <v>9.57634630000001</v>
+        <v>7.44853750000001</v>
       </c>
       <c r="Q36">
-        <v>64.37634630000001</v>
+        <v>62.2485375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09765386401590578</v>
+        <v>0.09830775889630811</v>
       </c>
       <c r="T36">
-        <v>0.8021627848211303</v>
+        <v>0.8122783306574624</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.000281251033763</v>
+        <v>1.636547568306099</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08752504328260027</v>
+        <v>0.08764853631470274</v>
       </c>
       <c r="C37">
-        <v>239.0434114390741</v>
+        <v>233.0009245587407</v>
       </c>
       <c r="D37">
-        <v>369.1984114390741</v>
+        <v>368.1089245587407</v>
       </c>
       <c r="E37">
-        <v>-199.045</v>
+        <v>-194.092</v>
       </c>
       <c r="F37">
-        <v>173.355</v>
+        <v>178.308</v>
       </c>
       <c r="G37">
         <v>43.2</v>
@@ -4321,28 +4321,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M37">
-        <v>15.60195</v>
+        <v>16.04772</v>
       </c>
       <c r="N37">
-        <v>9.931383333333347</v>
+        <v>9.485613333333347</v>
       </c>
       <c r="O37">
-        <v>2.482845833333337</v>
+        <v>2.371403333333337</v>
       </c>
       <c r="P37">
-        <v>7.44853750000001</v>
+        <v>7.114210000000011</v>
       </c>
       <c r="Q37">
-        <v>62.2485375</v>
+        <v>61.91421000000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09830775889630811</v>
+        <v>0.09898208799172303</v>
       </c>
       <c r="T37">
-        <v>0.8122783306574624</v>
+        <v>0.8227099873011797</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.636547568306099</v>
+        <v>1.59108791363093</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08764853631470275</v>
+        <v>0.0877720293468052</v>
       </c>
       <c r="C38">
-        <v>233.0009245587406</v>
+        <v>226.9648488069795</v>
       </c>
       <c r="D38">
-        <v>368.1089245587406</v>
+        <v>367.0258488069795</v>
       </c>
       <c r="E38">
-        <v>-194.092</v>
+        <v>-189.139</v>
       </c>
       <c r="F38">
-        <v>178.308</v>
+        <v>183.261</v>
       </c>
       <c r="G38">
         <v>43.2</v>
@@ -4403,28 +4403,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M38">
-        <v>16.04771999999999</v>
+        <v>16.49349</v>
       </c>
       <c r="N38">
-        <v>9.485613333333351</v>
+        <v>9.039843333333348</v>
       </c>
       <c r="O38">
-        <v>2.371403333333338</v>
+        <v>2.259960833333337</v>
       </c>
       <c r="P38">
-        <v>7.114210000000013</v>
+        <v>6.779882500000011</v>
       </c>
       <c r="Q38">
-        <v>61.91421000000001</v>
+        <v>61.57988250000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09898208799172303</v>
+        <v>0.09967782436000826</v>
       </c>
       <c r="T38">
-        <v>0.8227099873011797</v>
+        <v>0.8334728076478722</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.59108791363093</v>
+        <v>1.548085537586851</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0877720293468052</v>
+        <v>0.08789552237890767</v>
       </c>
       <c r="C39">
-        <v>226.9648488069795</v>
+        <v>220.9351277599954</v>
       </c>
       <c r="D39">
-        <v>367.0258488069795</v>
+        <v>365.9491277599954</v>
       </c>
       <c r="E39">
-        <v>-189.139</v>
+        <v>-184.186</v>
       </c>
       <c r="F39">
-        <v>183.261</v>
+        <v>188.214</v>
       </c>
       <c r="G39">
         <v>43.2</v>
@@ -4485,28 +4485,28 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M39">
-        <v>16.49349</v>
+        <v>16.93926</v>
       </c>
       <c r="N39">
-        <v>9.039843333333348</v>
+        <v>8.594073333333345</v>
       </c>
       <c r="O39">
-        <v>2.259960833333337</v>
+        <v>2.148518333333336</v>
       </c>
       <c r="P39">
-        <v>6.779882500000011</v>
+        <v>6.445555000000009</v>
       </c>
       <c r="Q39">
-        <v>61.57988250000001</v>
+        <v>61.245555</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09967782436000826</v>
+        <v>0.1003960038369479</v>
       </c>
       <c r="T39">
-        <v>0.8334728076478722</v>
+        <v>0.8445828157476839</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.548085537586851</v>
+        <v>1.50734644449246</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08789552237890767</v>
+        <v>0.1064213231993595</v>
       </c>
       <c r="C40">
-        <v>220.9351277599954</v>
+        <v>104.14853038033</v>
       </c>
       <c r="D40">
-        <v>365.9491277599954</v>
+        <v>254.11553038033</v>
       </c>
       <c r="E40">
-        <v>-184.186</v>
+        <v>-179.233</v>
       </c>
       <c r="F40">
-        <v>188.214</v>
+        <v>193.167</v>
       </c>
       <c r="G40">
         <v>43.2</v>
@@ -4567,45 +4567,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M40">
-        <v>16.93926</v>
+        <v>28.3569156</v>
       </c>
       <c r="N40">
-        <v>8.594073333333345</v>
+        <v>-2.823582266666659</v>
       </c>
       <c r="O40">
-        <v>2.148518333333336</v>
+        <v>-0.7058955666666646</v>
       </c>
       <c r="P40">
-        <v>6.445555000000009</v>
+        <v>-2.117686699999994</v>
       </c>
       <c r="Q40">
-        <v>61.245555</v>
+        <v>52.6823133</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1003960038369479</v>
+        <v>0.1017330086881475</v>
       </c>
       <c r="T40">
-        <v>0.8445828157476839</v>
+        <v>0.8652658555772464</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.25</v>
+        <v>0.2251067578496914</v>
       </c>
       <c r="W40">
-        <v>0.0675</v>
+        <v>0.1137543279476653</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.50734644449246</v>
+        <v>0.9004270313987655</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1064213231993595</v>
+        <v>0.1074313231993595</v>
       </c>
       <c r="C41">
-        <v>104.14853038033</v>
+        <v>95.03114330634281</v>
       </c>
       <c r="D41">
-        <v>254.11553038033</v>
+        <v>249.9511433063428</v>
       </c>
       <c r="E41">
-        <v>-179.233</v>
+        <v>-174.28</v>
       </c>
       <c r="F41">
-        <v>193.167</v>
+        <v>198.12</v>
       </c>
       <c r="G41">
         <v>43.2</v>
@@ -4649,37 +4649,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M41">
-        <v>28.3569156</v>
+        <v>29.084016</v>
       </c>
       <c r="N41">
-        <v>-2.823582266666659</v>
+        <v>-3.550682666666656</v>
       </c>
       <c r="O41">
-        <v>-0.7058955666666646</v>
+        <v>-0.8876706666666641</v>
       </c>
       <c r="P41">
-        <v>-2.117686699999994</v>
+        <v>-2.663011999999992</v>
       </c>
       <c r="Q41">
-        <v>52.6823133</v>
+        <v>52.136988</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1017330086881475</v>
+        <v>0.1026652254996167</v>
       </c>
       <c r="T41">
-        <v>0.8652658555772464</v>
+        <v>0.8796869531702004</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2251067578496914</v>
+        <v>0.2194790889034491</v>
       </c>
       <c r="W41">
-        <v>0.1137543279476653</v>
+        <v>0.1145804697489737</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9004270313987655</v>
+        <v>0.8779163556137963</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1074313231993595</v>
+        <v>0.1084413231993595</v>
       </c>
       <c r="C42">
-        <v>95.03114330634281</v>
+        <v>86.04804557140253</v>
       </c>
       <c r="D42">
-        <v>249.9511433063428</v>
+        <v>245.9210455714025</v>
       </c>
       <c r="E42">
-        <v>-174.28</v>
+        <v>-169.327</v>
       </c>
       <c r="F42">
-        <v>198.12</v>
+        <v>203.073</v>
       </c>
       <c r="G42">
         <v>43.2</v>
@@ -4731,37 +4731,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M42">
-        <v>29.084016</v>
+        <v>29.8111164</v>
       </c>
       <c r="N42">
-        <v>-3.550682666666656</v>
+        <v>-4.277783066666657</v>
       </c>
       <c r="O42">
-        <v>-0.8876706666666641</v>
+        <v>-1.069445766666664</v>
       </c>
       <c r="P42">
-        <v>-2.663011999999992</v>
+        <v>-3.208337299999993</v>
       </c>
       <c r="Q42">
-        <v>52.136988</v>
+        <v>51.5916627</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1026652254996167</v>
+        <v>0.1036290428809661</v>
       </c>
       <c r="T42">
-        <v>0.8796869531702004</v>
+        <v>0.8945969015290174</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2194790889034491</v>
+        <v>0.2141259403936089</v>
       </c>
       <c r="W42">
-        <v>0.1145804697489737</v>
+        <v>0.1153663119502182</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8779163556137963</v>
+        <v>0.8565037615744355</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1084413231993595</v>
+        <v>0.1094513231993595</v>
       </c>
       <c r="C43">
-        <v>86.04804557140253</v>
+        <v>77.19284458731335</v>
       </c>
       <c r="D43">
-        <v>245.9210455714025</v>
+        <v>242.0188445873133</v>
       </c>
       <c r="E43">
-        <v>-169.327</v>
+        <v>-164.374</v>
       </c>
       <c r="F43">
-        <v>203.073</v>
+        <v>208.026</v>
       </c>
       <c r="G43">
         <v>43.2</v>
@@ -4813,37 +4813,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M43">
-        <v>29.8111164</v>
+        <v>30.5382168</v>
       </c>
       <c r="N43">
-        <v>-4.277783066666657</v>
+        <v>-5.004883466666659</v>
       </c>
       <c r="O43">
-        <v>-1.069445766666664</v>
+        <v>-1.251220866666665</v>
       </c>
       <c r="P43">
-        <v>-3.208337299999993</v>
+        <v>-3.753662599999994</v>
       </c>
       <c r="Q43">
-        <v>51.5916627</v>
+        <v>51.04633740000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1036290428809661</v>
+        <v>0.104626095344431</v>
       </c>
       <c r="T43">
-        <v>0.8945969015290174</v>
+        <v>0.9100209860381385</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2141259403936089</v>
+        <v>0.2090277037175705</v>
       </c>
       <c r="W43">
-        <v>0.1153663119502182</v>
+        <v>0.1161147330942607</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8565037615744355</v>
+        <v>0.8361108148702823</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1094513231993595</v>
+        <v>0.1104613231993595</v>
       </c>
       <c r="C44">
-        <v>77.19284458731337</v>
+        <v>68.4595471708879</v>
       </c>
       <c r="D44">
-        <v>242.0188445873133</v>
+        <v>238.2385471708879</v>
       </c>
       <c r="E44">
-        <v>-164.374</v>
+        <v>-159.421</v>
       </c>
       <c r="F44">
-        <v>208.026</v>
+        <v>212.979</v>
       </c>
       <c r="G44">
         <v>43.2</v>
@@ -4895,37 +4895,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M44">
-        <v>30.5382168</v>
+        <v>31.2653172</v>
       </c>
       <c r="N44">
-        <v>-5.004883466666655</v>
+        <v>-5.731983866666656</v>
       </c>
       <c r="O44">
-        <v>-1.251220866666664</v>
+        <v>-1.432995966666664</v>
       </c>
       <c r="P44">
-        <v>-3.753662599999991</v>
+        <v>-4.298987899999992</v>
       </c>
       <c r="Q44">
-        <v>51.04633740000001</v>
+        <v>50.5010121</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.104626095344431</v>
+        <v>0.1056581321048596</v>
       </c>
       <c r="T44">
-        <v>0.9100209860381384</v>
+        <v>0.9259862664949478</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2090277037175706</v>
+        <v>0.2041665943287899</v>
       </c>
       <c r="W44">
-        <v>0.1161147330942607</v>
+        <v>0.1168283439525337</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8361108148702823</v>
+        <v>0.8166663773151595</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1104613231993595</v>
+        <v>0.136114376986208</v>
       </c>
       <c r="C45">
-        <v>68.4595471708879</v>
+        <v>-4.163146942251302</v>
       </c>
       <c r="D45">
-        <v>238.2385471708879</v>
+        <v>170.5688530577487</v>
       </c>
       <c r="E45">
-        <v>-159.421</v>
+        <v>-154.468</v>
       </c>
       <c r="F45">
-        <v>212.979</v>
+        <v>217.932</v>
       </c>
       <c r="G45">
         <v>43.2</v>
@@ -4977,45 +4977,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M45">
-        <v>31.2653172</v>
+        <v>43.7607456</v>
       </c>
       <c r="N45">
-        <v>-5.731983866666656</v>
+        <v>-18.22741226666665</v>
       </c>
       <c r="O45">
-        <v>-1.432995966666664</v>
+        <v>-4.556853066666664</v>
       </c>
       <c r="P45">
-        <v>-4.298987899999992</v>
+        <v>-13.67055919999999</v>
       </c>
       <c r="Q45">
-        <v>50.5010121</v>
+        <v>41.1294408</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1056581321048596</v>
+        <v>0.1083039090832473</v>
       </c>
       <c r="T45">
-        <v>0.9259862664949478</v>
+        <v>0.9669155948926939</v>
       </c>
       <c r="U45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.2041665943287899</v>
+        <v>0.145868934493962</v>
       </c>
       <c r="W45">
-        <v>0.1168283439525337</v>
+        <v>0.1715095179536124</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8166663773151595</v>
+        <v>0.5834757379758481</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.136114376986208</v>
+        <v>0.137664376986208</v>
       </c>
       <c r="C46">
-        <v>-4.163146942251302</v>
+        <v>-11.99410389262823</v>
       </c>
       <c r="D46">
-        <v>170.5688530577487</v>
+        <v>167.6908961073717</v>
       </c>
       <c r="E46">
-        <v>-154.468</v>
+        <v>-149.515</v>
       </c>
       <c r="F46">
-        <v>217.932</v>
+        <v>222.885</v>
       </c>
       <c r="G46">
         <v>43.2</v>
@@ -5059,37 +5059,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M46">
-        <v>43.7607456</v>
+        <v>44.755308</v>
       </c>
       <c r="N46">
-        <v>-18.22741226666665</v>
+        <v>-19.22197466666665</v>
       </c>
       <c r="O46">
-        <v>-4.556853066666664</v>
+        <v>-4.805493666666663</v>
       </c>
       <c r="P46">
-        <v>-13.67055919999999</v>
+        <v>-14.41648099999999</v>
       </c>
       <c r="Q46">
-        <v>41.1294408</v>
+        <v>40.38351900000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1083039090832473</v>
+        <v>0.1094403437938518</v>
       </c>
       <c r="T46">
-        <v>0.9669155948926939</v>
+        <v>0.9844958784361973</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.145868934493962</v>
+        <v>0.1426274026163184</v>
       </c>
       <c r="W46">
-        <v>0.1715095179536124</v>
+        <v>0.1721604175546433</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5834757379758481</v>
+        <v>0.5705096104652736</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.137664376986208</v>
+        <v>0.1392143769862079</v>
       </c>
       <c r="C47">
-        <v>-11.99410389262823</v>
+        <v>-19.72955448912265</v>
       </c>
       <c r="D47">
-        <v>167.6908961073717</v>
+        <v>164.9084455108774</v>
       </c>
       <c r="E47">
-        <v>-149.515</v>
+        <v>-144.562</v>
       </c>
       <c r="F47">
-        <v>222.885</v>
+        <v>227.838</v>
       </c>
       <c r="G47">
         <v>43.2</v>
@@ -5141,37 +5141,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M47">
-        <v>44.755308</v>
+        <v>45.7498704</v>
       </c>
       <c r="N47">
-        <v>-19.22197466666665</v>
+        <v>-20.21653706666665</v>
       </c>
       <c r="O47">
-        <v>-4.805493666666663</v>
+        <v>-5.054134266666663</v>
       </c>
       <c r="P47">
-        <v>-14.41648099999999</v>
+        <v>-15.16240279999999</v>
       </c>
       <c r="Q47">
-        <v>40.38351900000001</v>
+        <v>39.63759720000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1094403437938518</v>
+        <v>0.1106188686789231</v>
       </c>
       <c r="T47">
-        <v>0.9844958784361973</v>
+        <v>1.002727283592423</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1426274026163184</v>
+        <v>0.139526806907268</v>
       </c>
       <c r="W47">
-        <v>0.1721604175546433</v>
+        <v>0.1727830171730206</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5705096104652736</v>
+        <v>0.5581072276290721</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1392143769862079</v>
+        <v>0.1407643769862079</v>
       </c>
       <c r="C48">
-        <v>-19.72955448912265</v>
+        <v>-27.37417527002856</v>
       </c>
       <c r="D48">
-        <v>164.9084455108774</v>
+        <v>162.2168247299714</v>
       </c>
       <c r="E48">
-        <v>-144.562</v>
+        <v>-139.609</v>
       </c>
       <c r="F48">
-        <v>227.838</v>
+        <v>232.791</v>
       </c>
       <c r="G48">
         <v>43.2</v>
@@ -5223,37 +5223,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M48">
-        <v>45.7498704</v>
+        <v>46.7444328</v>
       </c>
       <c r="N48">
-        <v>-20.21653706666665</v>
+        <v>-21.21109946666665</v>
       </c>
       <c r="O48">
-        <v>-5.054134266666663</v>
+        <v>-5.302774866666663</v>
       </c>
       <c r="P48">
-        <v>-15.16240279999999</v>
+        <v>-15.90832459999999</v>
       </c>
       <c r="Q48">
-        <v>39.63759720000001</v>
+        <v>38.89167540000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1106188686789231</v>
+        <v>0.1118418662011669</v>
       </c>
       <c r="T48">
-        <v>1.002727283592423</v>
+        <v>1.021646666301714</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.139526806907268</v>
+        <v>0.1365581514411559</v>
       </c>
       <c r="W48">
-        <v>0.1727830171730206</v>
+        <v>0.1733791231906159</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5581072276290721</v>
+        <v>0.5462326057646237</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1407643769862079</v>
+        <v>0.1423143769862079</v>
       </c>
       <c r="C49">
-        <v>-27.37417527002856</v>
+        <v>-34.93234235686978</v>
       </c>
       <c r="D49">
-        <v>162.2168247299714</v>
+        <v>159.6116576431302</v>
       </c>
       <c r="E49">
-        <v>-139.609</v>
+        <v>-134.656</v>
       </c>
       <c r="F49">
-        <v>232.791</v>
+        <v>237.744</v>
       </c>
       <c r="G49">
         <v>43.2</v>
@@ -5305,37 +5305,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M49">
-        <v>46.7444328</v>
+        <v>47.7389952</v>
       </c>
       <c r="N49">
-        <v>-21.21109946666665</v>
+        <v>-22.20566186666665</v>
       </c>
       <c r="O49">
-        <v>-5.302774866666663</v>
+        <v>-5.551415466666663</v>
       </c>
       <c r="P49">
-        <v>-15.90832459999999</v>
+        <v>-16.65424639999999</v>
       </c>
       <c r="Q49">
-        <v>38.89167540000001</v>
+        <v>38.14575360000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1118418662011669</v>
+        <v>0.1131119020896509</v>
       </c>
       <c r="T49">
-        <v>1.021646666301714</v>
+        <v>1.041293717576747</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1365581514411559</v>
+        <v>0.1337131899527985</v>
       </c>
       <c r="W49">
-        <v>0.1733791231906159</v>
+        <v>0.1739503914574781</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5462326057646237</v>
+        <v>0.5348527598111941</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1423143769862079</v>
+        <v>0.1438643769862079</v>
       </c>
       <c r="C50">
-        <v>-34.93234235686975</v>
+        <v>-42.40815519625224</v>
       </c>
       <c r="D50">
-        <v>159.6116576431302</v>
+        <v>157.0888448037477</v>
       </c>
       <c r="E50">
-        <v>-134.656</v>
+        <v>-129.703</v>
       </c>
       <c r="F50">
-        <v>237.744</v>
+        <v>242.697</v>
       </c>
       <c r="G50">
         <v>43.2</v>
@@ -5387,37 +5387,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M50">
-        <v>47.7389952</v>
+        <v>48.7335576</v>
       </c>
       <c r="N50">
-        <v>-22.20566186666665</v>
+        <v>-23.20022426666665</v>
       </c>
       <c r="O50">
-        <v>-5.551415466666663</v>
+        <v>-5.800056066666663</v>
       </c>
       <c r="P50">
-        <v>-16.65424639999999</v>
+        <v>-17.40016819999999</v>
       </c>
       <c r="Q50">
-        <v>38.14575360000001</v>
+        <v>37.39983180000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1131119020896509</v>
+        <v>0.114431743307095</v>
       </c>
       <c r="T50">
-        <v>1.041293717576747</v>
+        <v>1.061711241450801</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1337131899527985</v>
+        <v>0.1309843493415169</v>
       </c>
       <c r="W50">
-        <v>0.1739503914574781</v>
+        <v>0.1744983426522234</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5348527598111941</v>
+        <v>0.5239373973660677</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1438643769862079</v>
+        <v>0.1454143769862079</v>
       </c>
       <c r="C51">
-        <v>-42.40815519625224</v>
+        <v>-49.80545808517678</v>
       </c>
       <c r="D51">
-        <v>157.0888448037477</v>
+        <v>154.6445419148232</v>
       </c>
       <c r="E51">
-        <v>-129.703</v>
+        <v>-124.75</v>
       </c>
       <c r="F51">
-        <v>242.697</v>
+        <v>247.65</v>
       </c>
       <c r="G51">
         <v>43.2</v>
@@ -5469,37 +5469,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M51">
-        <v>48.7335576</v>
+        <v>49.72812</v>
       </c>
       <c r="N51">
-        <v>-23.20022426666665</v>
+        <v>-24.19478666666665</v>
       </c>
       <c r="O51">
-        <v>-5.800056066666663</v>
+        <v>-6.048696666666663</v>
       </c>
       <c r="P51">
-        <v>-17.40016819999999</v>
+        <v>-18.14608999999999</v>
       </c>
       <c r="Q51">
-        <v>37.39983180000001</v>
+        <v>36.65391000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.114431743307095</v>
+        <v>0.1158043781732369</v>
       </c>
       <c r="T51">
-        <v>1.061711241450801</v>
+        <v>1.082945466279817</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1309843493415169</v>
+        <v>0.1283646623546866</v>
       </c>
       <c r="W51">
-        <v>0.1744983426522234</v>
+        <v>0.1750243757991789</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5239373973660677</v>
+        <v>0.5134586494187463</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1454143769862079</v>
+        <v>0.146964376986208</v>
       </c>
       <c r="C52">
-        <v>-49.80545808517678</v>
+        <v>-57.12785971753854</v>
       </c>
       <c r="D52">
-        <v>154.6445419148232</v>
+        <v>152.2751402824614</v>
       </c>
       <c r="E52">
-        <v>-124.75</v>
+        <v>-119.797</v>
       </c>
       <c r="F52">
-        <v>247.65</v>
+        <v>252.603</v>
       </c>
       <c r="G52">
         <v>43.2</v>
@@ -5551,37 +5551,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M52">
-        <v>49.72812</v>
+        <v>50.7226824</v>
       </c>
       <c r="N52">
-        <v>-24.19478666666665</v>
+        <v>-25.18934906666665</v>
       </c>
       <c r="O52">
-        <v>-6.048696666666663</v>
+        <v>-6.297337266666663</v>
       </c>
       <c r="P52">
-        <v>-18.14608999999999</v>
+        <v>-18.89201179999999</v>
       </c>
       <c r="Q52">
-        <v>36.65391000000001</v>
+        <v>35.90798820000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1158043781732369</v>
+        <v>0.1172330389522826</v>
       </c>
       <c r="T52">
-        <v>1.082945466279817</v>
+        <v>1.105046394163079</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1283646623546866</v>
+        <v>0.1258477081908692</v>
       </c>
       <c r="W52">
-        <v>0.1750243757991789</v>
+        <v>0.1755297801952735</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5134586494187463</v>
+        <v>0.5033908327634768</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.146964376986208</v>
+        <v>0.1670706998553082</v>
       </c>
       <c r="C53">
-        <v>-57.12785971753854</v>
+        <v>-87.32762698374302</v>
       </c>
       <c r="D53">
-        <v>152.2751402824614</v>
+        <v>127.0283730162569</v>
       </c>
       <c r="E53">
-        <v>-119.797</v>
+        <v>-114.844</v>
       </c>
       <c r="F53">
-        <v>252.603</v>
+        <v>257.556</v>
       </c>
       <c r="G53">
         <v>43.2</v>
@@ -5633,45 +5633,45 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M53">
-        <v>50.7226824</v>
+        <v>60.7317048</v>
       </c>
       <c r="N53">
-        <v>-25.18934906666665</v>
+        <v>-35.19837146666665</v>
       </c>
       <c r="O53">
-        <v>-6.297337266666663</v>
+        <v>-8.799592866666663</v>
       </c>
       <c r="P53">
-        <v>-18.89201179999999</v>
+        <v>-26.39877859999999</v>
       </c>
       <c r="Q53">
-        <v>35.90798820000001</v>
+        <v>28.40122140000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1172330389522826</v>
+        <v>0.1194635665744141</v>
       </c>
       <c r="T53">
-        <v>1.105046394163079</v>
+        <v>1.139551947084662</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1258477081908692</v>
+        <v>0.1051070994031002</v>
       </c>
       <c r="W53">
-        <v>0.1755297801952735</v>
+        <v>0.211015745960749</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5033908327634768</v>
+        <v>0.4204283976124008</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1670706998553082</v>
+        <v>0.1689706998553082</v>
       </c>
       <c r="C54">
-        <v>-87.32762698374302</v>
+        <v>-94.24013447224814</v>
       </c>
       <c r="D54">
-        <v>127.0283730162569</v>
+        <v>125.0688655277519</v>
       </c>
       <c r="E54">
-        <v>-114.844</v>
+        <v>-109.891</v>
       </c>
       <c r="F54">
-        <v>257.556</v>
+        <v>262.509</v>
       </c>
       <c r="G54">
         <v>43.2</v>
@@ -5715,37 +5715,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M54">
-        <v>60.7317048</v>
+        <v>61.8996222</v>
       </c>
       <c r="N54">
-        <v>-35.19837146666665</v>
+        <v>-36.36628886666666</v>
       </c>
       <c r="O54">
-        <v>-8.799592866666663</v>
+        <v>-9.091572216666664</v>
       </c>
       <c r="P54">
-        <v>-26.39877859999999</v>
+        <v>-27.27471664999999</v>
       </c>
       <c r="Q54">
-        <v>28.40122140000001</v>
+        <v>27.52528335</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1194635665744141</v>
+        <v>0.1210308765015292</v>
       </c>
       <c r="T54">
-        <v>1.139551947084662</v>
+        <v>1.163797733192846</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1051070994031002</v>
+        <v>0.1031239465841738</v>
       </c>
       <c r="W54">
-        <v>0.211015745960749</v>
+        <v>0.2114833733954518</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4204283976124008</v>
+        <v>0.412495786336695</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1689706998553082</v>
+        <v>0.1708706998553082</v>
       </c>
       <c r="C55">
-        <v>-94.24013447224814</v>
+        <v>-101.0931066062303</v>
       </c>
       <c r="D55">
-        <v>125.0688655277519</v>
+        <v>123.1688933937697</v>
       </c>
       <c r="E55">
-        <v>-109.891</v>
+        <v>-104.938</v>
       </c>
       <c r="F55">
-        <v>262.509</v>
+        <v>267.462</v>
       </c>
       <c r="G55">
         <v>43.2</v>
@@ -5797,37 +5797,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M55">
-        <v>61.8996222</v>
+        <v>63.0675396</v>
       </c>
       <c r="N55">
-        <v>-36.36628886666666</v>
+        <v>-37.53420626666666</v>
       </c>
       <c r="O55">
-        <v>-9.091572216666664</v>
+        <v>-9.383551566666664</v>
       </c>
       <c r="P55">
-        <v>-27.27471664999999</v>
+        <v>-28.15065469999999</v>
       </c>
       <c r="Q55">
-        <v>27.52528335</v>
+        <v>26.6493453</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1210308765015292</v>
+        <v>0.122666330338519</v>
       </c>
       <c r="T55">
-        <v>1.163797733192846</v>
+        <v>1.18909768391443</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1031239465841738</v>
+        <v>0.101214243869652</v>
       </c>
       <c r="W55">
-        <v>0.2114833733954518</v>
+        <v>0.2119336812955361</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.412495786336695</v>
+        <v>0.4048569754786081</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1708706998553082</v>
+        <v>0.1727706998553082</v>
       </c>
       <c r="C56">
-        <v>-101.0931066062303</v>
+        <v>-107.8892160615208</v>
       </c>
       <c r="D56">
-        <v>123.1688933937697</v>
+        <v>121.3257839384792</v>
       </c>
       <c r="E56">
-        <v>-104.938</v>
+        <v>-99.98499999999996</v>
       </c>
       <c r="F56">
-        <v>267.462</v>
+        <v>272.415</v>
       </c>
       <c r="G56">
         <v>43.2</v>
@@ -5879,37 +5879,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M56">
-        <v>63.0675396</v>
+        <v>64.23545700000001</v>
       </c>
       <c r="N56">
-        <v>-37.53420626666666</v>
+        <v>-38.70212366666667</v>
       </c>
       <c r="O56">
-        <v>-9.383551566666664</v>
+        <v>-9.675530916666666</v>
       </c>
       <c r="P56">
-        <v>-28.15065469999999</v>
+        <v>-29.02659275</v>
       </c>
       <c r="Q56">
-        <v>26.6493453</v>
+        <v>25.77340725</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.122666330338519</v>
+        <v>0.1243744710127083</v>
       </c>
       <c r="T56">
-        <v>1.18909768391443</v>
+        <v>1.215522076890306</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.101214243869652</v>
+        <v>0.09937398489020378</v>
       </c>
       <c r="W56">
-        <v>0.2119336812955361</v>
+        <v>0.21236761436289</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4048569754786081</v>
+        <v>0.3974959395608152</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1727706998553082</v>
+        <v>0.1746706998553082</v>
       </c>
       <c r="C57">
-        <v>-107.8892160615208</v>
+        <v>-114.6309778959946</v>
       </c>
       <c r="D57">
-        <v>121.3257839384792</v>
+        <v>119.5370221040054</v>
       </c>
       <c r="E57">
-        <v>-99.98499999999996</v>
+        <v>-95.03199999999998</v>
       </c>
       <c r="F57">
-        <v>272.415</v>
+        <v>277.368</v>
       </c>
       <c r="G57">
         <v>43.2</v>
@@ -5961,37 +5961,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M57">
-        <v>64.23545700000001</v>
+        <v>65.4033744</v>
       </c>
       <c r="N57">
-        <v>-38.70212366666667</v>
+        <v>-39.87004106666666</v>
       </c>
       <c r="O57">
-        <v>-9.675530916666666</v>
+        <v>-9.967510266666665</v>
       </c>
       <c r="P57">
-        <v>-29.02659275</v>
+        <v>-29.90253079999999</v>
       </c>
       <c r="Q57">
-        <v>25.77340725</v>
+        <v>24.8974692</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1243744710127083</v>
+        <v>0.1261602544448153</v>
       </c>
       <c r="T57">
-        <v>1.215522076890306</v>
+        <v>1.243147578637813</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09937398489020378</v>
+        <v>0.09759944944573587</v>
       </c>
       <c r="W57">
-        <v>0.21236761436289</v>
+        <v>0.2127860498206955</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3974959395608152</v>
+        <v>0.3903977977829435</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1746706998553082</v>
+        <v>0.1765706998553082</v>
       </c>
       <c r="C58">
-        <v>-114.6309778959946</v>
+        <v>-121.3207609999232</v>
       </c>
       <c r="D58">
-        <v>119.5370221040054</v>
+        <v>117.8002390000769</v>
       </c>
       <c r="E58">
-        <v>-95.03199999999998</v>
+        <v>-90.07899999999995</v>
       </c>
       <c r="F58">
-        <v>277.368</v>
+        <v>282.321</v>
       </c>
       <c r="G58">
         <v>43.2</v>
@@ -6043,37 +6043,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M58">
-        <v>65.4033744</v>
+        <v>66.57129180000001</v>
       </c>
       <c r="N58">
-        <v>-39.87004106666666</v>
+        <v>-41.03795846666667</v>
       </c>
       <c r="O58">
-        <v>-9.967510266666665</v>
+        <v>-10.25948961666667</v>
       </c>
       <c r="P58">
-        <v>-29.90253079999999</v>
+        <v>-30.77846885</v>
       </c>
       <c r="Q58">
-        <v>24.8974692</v>
+        <v>24.02153115</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1261602544448153</v>
+        <v>0.128029097571439</v>
       </c>
       <c r="T58">
-        <v>1.243147578637813</v>
+        <v>1.272057987443344</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09759944944573587</v>
+        <v>0.09588717840282822</v>
       </c>
       <c r="W58">
-        <v>0.2127860498206955</v>
+        <v>0.2131898033326131</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3903977977829435</v>
+        <v>0.3835487136113129</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1765706998553082</v>
+        <v>0.1784706998553082</v>
       </c>
       <c r="C59">
-        <v>-121.3207609999232</v>
+        <v>-127.9607985624312</v>
       </c>
       <c r="D59">
-        <v>117.8002390000769</v>
+        <v>116.1132014375688</v>
       </c>
       <c r="E59">
-        <v>-90.07899999999995</v>
+        <v>-85.12599999999998</v>
       </c>
       <c r="F59">
-        <v>282.321</v>
+        <v>287.274</v>
       </c>
       <c r="G59">
         <v>43.2</v>
@@ -6125,37 +6125,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M59">
-        <v>66.57129180000001</v>
+        <v>67.7392092</v>
       </c>
       <c r="N59">
-        <v>-41.03795846666667</v>
+        <v>-42.20587586666666</v>
       </c>
       <c r="O59">
-        <v>-10.25948961666667</v>
+        <v>-10.55146896666666</v>
       </c>
       <c r="P59">
-        <v>-30.77846885</v>
+        <v>-31.65440689999999</v>
       </c>
       <c r="Q59">
-        <v>24.02153115</v>
+        <v>23.1455931</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.128029097571439</v>
+        <v>0.1299869332279018</v>
       </c>
       <c r="T59">
-        <v>1.272057987443344</v>
+        <v>1.302345082382471</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09588717840282822</v>
+        <v>0.09423395118898636</v>
       </c>
       <c r="W59">
-        <v>0.2131898033326131</v>
+        <v>0.213579634309637</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3835487136113129</v>
+        <v>0.3769358047559455</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1784706998553082</v>
+        <v>0.1803706998553082</v>
       </c>
       <c r="C60">
-        <v>-127.9607985624312</v>
+        <v>-134.5531976513012</v>
       </c>
       <c r="D60">
-        <v>116.1132014375688</v>
+        <v>114.4738023486988</v>
       </c>
       <c r="E60">
-        <v>-85.12600000000003</v>
+        <v>-80.173</v>
       </c>
       <c r="F60">
-        <v>287.2739999999999</v>
+        <v>292.227</v>
       </c>
       <c r="G60">
         <v>43.2</v>
@@ -6207,37 +6207,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M60">
-        <v>67.73920919999999</v>
+        <v>68.9071266</v>
       </c>
       <c r="N60">
-        <v>-42.20587586666664</v>
+        <v>-43.37379326666665</v>
       </c>
       <c r="O60">
-        <v>-10.55146896666666</v>
+        <v>-10.84344831666666</v>
       </c>
       <c r="P60">
-        <v>-31.65440689999998</v>
+        <v>-32.53034494999999</v>
       </c>
       <c r="Q60">
-        <v>23.14559310000001</v>
+        <v>22.26965505000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1299869332279018</v>
+        <v>0.1320402730627286</v>
       </c>
       <c r="T60">
-        <v>1.30234508238247</v>
+        <v>1.334109596586921</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09423395118898638</v>
+        <v>0.09263676557561372</v>
       </c>
       <c r="W60">
-        <v>0.213579634309637</v>
+        <v>0.2139562506772703</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3769358047559456</v>
+        <v>0.3705470623024549</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1803706998553082</v>
+        <v>0.1822706998553082</v>
       </c>
       <c r="C61">
-        <v>-134.5531976513012</v>
+        <v>-141.0999479925328</v>
       </c>
       <c r="D61">
-        <v>114.4738023486988</v>
+        <v>112.8800520074671</v>
       </c>
       <c r="E61">
-        <v>-80.173</v>
+        <v>-75.22000000000003</v>
       </c>
       <c r="F61">
-        <v>292.227</v>
+        <v>297.1799999999999</v>
       </c>
       <c r="G61">
         <v>43.2</v>
@@ -6289,37 +6289,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M61">
-        <v>68.9071266</v>
+        <v>70.07504399999999</v>
       </c>
       <c r="N61">
-        <v>-43.37379326666665</v>
+        <v>-44.54171066666665</v>
       </c>
       <c r="O61">
-        <v>-10.84344831666666</v>
+        <v>-11.13542766666666</v>
       </c>
       <c r="P61">
-        <v>-32.53034494999999</v>
+        <v>-33.40628299999999</v>
       </c>
       <c r="Q61">
-        <v>22.26965505000001</v>
+        <v>21.39371700000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1320402730627286</v>
+        <v>0.1341962798892969</v>
       </c>
       <c r="T61">
-        <v>1.334109596586921</v>
+        <v>1.367462336501594</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09263676557561372</v>
+        <v>0.09109281948268684</v>
       </c>
       <c r="W61">
-        <v>0.2139562506772703</v>
+        <v>0.2143203131659824</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3705470623024549</v>
+        <v>0.3643712779307473</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1822706998553082</v>
+        <v>0.1841706998553082</v>
       </c>
       <c r="C62">
-        <v>-141.0999479925328</v>
+        <v>-147.6029300265795</v>
       </c>
       <c r="D62">
-        <v>112.8800520074671</v>
+        <v>111.3300699734205</v>
       </c>
       <c r="E62">
-        <v>-75.22000000000003</v>
+        <v>-70.267</v>
       </c>
       <c r="F62">
-        <v>297.1799999999999</v>
+        <v>302.133</v>
       </c>
       <c r="G62">
         <v>43.2</v>
@@ -6371,37 +6371,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M62">
-        <v>70.07504399999999</v>
+        <v>71.2429614</v>
       </c>
       <c r="N62">
-        <v>-44.54171066666665</v>
+        <v>-45.70962806666665</v>
       </c>
       <c r="O62">
-        <v>-11.13542766666666</v>
+        <v>-11.42740701666666</v>
       </c>
       <c r="P62">
-        <v>-33.40628299999999</v>
+        <v>-34.28222104999999</v>
       </c>
       <c r="Q62">
-        <v>21.39371700000001</v>
+        <v>20.51777895000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1341962798892969</v>
+        <v>0.1364628511685096</v>
       </c>
       <c r="T62">
-        <v>1.367462336501594</v>
+        <v>1.402525473334969</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09109281948268684</v>
+        <v>0.08959949457313458</v>
       </c>
       <c r="W62">
-        <v>0.2143203131659824</v>
+        <v>0.2146724391796549</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3643712779307473</v>
+        <v>0.3583979782925383</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1841706998553082</v>
+        <v>0.1860706998553082</v>
       </c>
       <c r="C63">
-        <v>-147.6029300265795</v>
+        <v>-154.063922309841</v>
       </c>
       <c r="D63">
-        <v>111.3300699734205</v>
+        <v>109.8220776901589</v>
       </c>
       <c r="E63">
-        <v>-70.267</v>
+        <v>-65.31400000000002</v>
       </c>
       <c r="F63">
-        <v>302.133</v>
+        <v>307.086</v>
       </c>
       <c r="G63">
         <v>43.2</v>
@@ -6453,37 +6453,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M63">
-        <v>71.2429614</v>
+        <v>72.41087879999999</v>
       </c>
       <c r="N63">
-        <v>-45.70962806666665</v>
+        <v>-46.87754546666665</v>
       </c>
       <c r="O63">
-        <v>-11.42740701666666</v>
+        <v>-11.71938636666666</v>
       </c>
       <c r="P63">
-        <v>-34.28222104999999</v>
+        <v>-35.15815909999998</v>
       </c>
       <c r="Q63">
-        <v>20.51777895000001</v>
+        <v>19.64184090000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1364628511685096</v>
+        <v>0.1388487156729441</v>
       </c>
       <c r="T63">
-        <v>1.402525473334969</v>
+        <v>1.439434038422731</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08959949457313458</v>
+        <v>0.08815434143485823</v>
       </c>
       <c r="W63">
-        <v>0.2146724391796549</v>
+        <v>0.2150132062896604</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3583979782925383</v>
+        <v>0.3526173657394329</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1860706998553082</v>
+        <v>0.1879706998553082</v>
       </c>
       <c r="C64">
-        <v>-154.063922309841</v>
+        <v>-160.4846083226669</v>
       </c>
       <c r="D64">
-        <v>109.8220776901589</v>
+        <v>108.3543916773331</v>
       </c>
       <c r="E64">
-        <v>-65.31400000000002</v>
+        <v>-60.36099999999999</v>
       </c>
       <c r="F64">
-        <v>307.086</v>
+        <v>312.039</v>
       </c>
       <c r="G64">
         <v>43.2</v>
@@ -6535,37 +6535,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M64">
-        <v>72.41087879999999</v>
+        <v>73.5787962</v>
       </c>
       <c r="N64">
-        <v>-46.87754546666665</v>
+        <v>-48.04546286666665</v>
       </c>
       <c r="O64">
-        <v>-11.71938636666666</v>
+        <v>-12.01136571666666</v>
       </c>
       <c r="P64">
-        <v>-35.15815909999998</v>
+        <v>-36.03409714999999</v>
       </c>
       <c r="Q64">
-        <v>19.64184090000001</v>
+        <v>18.76590285</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1388487156729441</v>
+        <v>0.1413635458262669</v>
       </c>
       <c r="T64">
-        <v>1.439434038422731</v>
+        <v>1.478337661082805</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08815434143485823</v>
+        <v>0.08675506617398746</v>
       </c>
       <c r="W64">
-        <v>0.2150132062896604</v>
+        <v>0.2153431553961738</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3526173657394329</v>
+        <v>0.3470202646959498</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1879706998553082</v>
+        <v>0.1898706998553082</v>
       </c>
       <c r="C65">
-        <v>-160.4846083226669</v>
+        <v>-166.8665827386563</v>
       </c>
       <c r="D65">
-        <v>108.3543916773331</v>
+        <v>106.9254172613436</v>
       </c>
       <c r="E65">
-        <v>-60.36099999999999</v>
+        <v>-55.40800000000002</v>
       </c>
       <c r="F65">
-        <v>312.039</v>
+        <v>316.992</v>
       </c>
       <c r="G65">
         <v>43.2</v>
@@ -6617,37 +6617,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M65">
-        <v>73.5787962</v>
+        <v>74.74671359999999</v>
       </c>
       <c r="N65">
-        <v>-48.04546286666665</v>
+        <v>-49.21338026666665</v>
       </c>
       <c r="O65">
-        <v>-12.01136571666666</v>
+        <v>-12.30334506666666</v>
       </c>
       <c r="P65">
-        <v>-36.03409714999999</v>
+        <v>-36.91003519999998</v>
       </c>
       <c r="Q65">
-        <v>18.76590285</v>
+        <v>17.88996480000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1413635458262669</v>
+        <v>0.1440180887658854</v>
       </c>
       <c r="T65">
-        <v>1.478337661082805</v>
+        <v>1.519402596112883</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08675506617398746</v>
+        <v>0.0853995182650189</v>
       </c>
       <c r="W65">
-        <v>0.2153431553961738</v>
+        <v>0.2156627935931086</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3470202646959498</v>
+        <v>0.3415980730600756</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1898706998553082</v>
+        <v>0.1917706998553082</v>
       </c>
       <c r="C66">
-        <v>-166.8665827386563</v>
+        <v>-173.2113572043398</v>
       </c>
       <c r="D66">
-        <v>106.9254172613436</v>
+        <v>105.5336427956602</v>
       </c>
       <c r="E66">
-        <v>-55.40800000000002</v>
+        <v>-50.45499999999998</v>
       </c>
       <c r="F66">
-        <v>316.992</v>
+        <v>321.945</v>
       </c>
       <c r="G66">
         <v>43.2</v>
@@ -6699,37 +6699,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M66">
-        <v>74.74671359999999</v>
+        <v>75.914631</v>
       </c>
       <c r="N66">
-        <v>-49.21338026666665</v>
+        <v>-50.38129766666665</v>
       </c>
       <c r="O66">
-        <v>-12.30334506666666</v>
+        <v>-12.59532441666666</v>
       </c>
       <c r="P66">
-        <v>-36.91003519999998</v>
+        <v>-37.78597324999999</v>
       </c>
       <c r="Q66">
-        <v>17.88996480000002</v>
+        <v>17.01402675000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1440180887658854</v>
+        <v>0.1468243198734821</v>
       </c>
       <c r="T66">
-        <v>1.519402596112883</v>
+        <v>1.562814098858965</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0853995182650189</v>
+        <v>0.08408567952248014</v>
       </c>
       <c r="W66">
-        <v>0.2156627935931086</v>
+        <v>0.2159725967685992</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3415980730600756</v>
+        <v>0.3363427180899206</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1917706998553082</v>
+        <v>0.1936706998553082</v>
       </c>
       <c r="C67">
-        <v>-173.2113572043398</v>
+        <v>-179.5203656732789</v>
       </c>
       <c r="D67">
-        <v>105.5336427956602</v>
+        <v>104.1776343267211</v>
       </c>
       <c r="E67">
-        <v>-50.45499999999998</v>
+        <v>-45.50200000000001</v>
       </c>
       <c r="F67">
-        <v>321.945</v>
+        <v>326.898</v>
       </c>
       <c r="G67">
         <v>43.2</v>
@@ -6781,37 +6781,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M67">
-        <v>75.914631</v>
+        <v>77.08254839999999</v>
       </c>
       <c r="N67">
-        <v>-50.38129766666665</v>
+        <v>-51.54921506666665</v>
       </c>
       <c r="O67">
-        <v>-12.59532441666666</v>
+        <v>-12.88730376666666</v>
       </c>
       <c r="P67">
-        <v>-37.78597324999999</v>
+        <v>-38.66191129999999</v>
       </c>
       <c r="Q67">
-        <v>17.01402675000001</v>
+        <v>16.13808870000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1468243198734821</v>
+        <v>0.1497956233991728</v>
       </c>
       <c r="T67">
-        <v>1.562814098858965</v>
+        <v>1.60877921941364</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08408567952248014</v>
+        <v>0.08281165407516984</v>
       </c>
       <c r="W67">
-        <v>0.2159725967685992</v>
+        <v>0.2162730119690749</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3363427180899206</v>
+        <v>0.3312466163006794</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1936706998553082</v>
+        <v>0.1955706998553083</v>
       </c>
       <c r="C68">
-        <v>-179.5203656732789</v>
+        <v>-185.7949693341552</v>
       </c>
       <c r="D68">
-        <v>104.1776343267211</v>
+        <v>102.8560306658449</v>
       </c>
       <c r="E68">
-        <v>-45.50200000000001</v>
+        <v>-40.54899999999998</v>
       </c>
       <c r="F68">
-        <v>326.898</v>
+        <v>331.851</v>
       </c>
       <c r="G68">
         <v>43.2</v>
@@ -6863,37 +6863,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M68">
-        <v>77.08254839999999</v>
+        <v>78.2504658</v>
       </c>
       <c r="N68">
-        <v>-51.54921506666665</v>
+        <v>-52.71713246666665</v>
       </c>
       <c r="O68">
-        <v>-12.88730376666666</v>
+        <v>-13.17928311666666</v>
       </c>
       <c r="P68">
-        <v>-38.66191129999999</v>
+        <v>-39.53784934999999</v>
       </c>
       <c r="Q68">
-        <v>16.13808870000001</v>
+        <v>15.26215065000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1497956233991728</v>
+        <v>0.1529470059264205</v>
       </c>
       <c r="T68">
-        <v>1.60877921941364</v>
+        <v>1.657530104850418</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08281165407516984</v>
+        <v>0.081575659238227</v>
       </c>
       <c r="W68">
-        <v>0.2162730119690749</v>
+        <v>0.2165644595516261</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3312466163006794</v>
+        <v>0.3263026369529081</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1955706998553083</v>
+        <v>0.1974706998553082</v>
       </c>
       <c r="C69">
-        <v>-185.7949693341552</v>
+        <v>-192.0364611684483</v>
       </c>
       <c r="D69">
-        <v>102.8560306658449</v>
+        <v>101.5675388315516</v>
       </c>
       <c r="E69">
-        <v>-40.54899999999998</v>
+        <v>-35.596</v>
       </c>
       <c r="F69">
-        <v>331.851</v>
+        <v>336.804</v>
       </c>
       <c r="G69">
         <v>43.2</v>
@@ -6945,37 +6945,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M69">
-        <v>78.2504658</v>
+        <v>79.41838319999999</v>
       </c>
       <c r="N69">
-        <v>-52.71713246666665</v>
+        <v>-53.88504986666665</v>
       </c>
       <c r="O69">
-        <v>-13.17928311666666</v>
+        <v>-13.47126246666666</v>
       </c>
       <c r="P69">
-        <v>-39.53784934999999</v>
+        <v>-40.41378739999999</v>
       </c>
       <c r="Q69">
-        <v>15.26215065000001</v>
+        <v>14.38621260000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1529470059264205</v>
+        <v>0.1562953498616211</v>
       </c>
       <c r="T69">
-        <v>1.657530104850418</v>
+        <v>1.709327920626993</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.081575659238227</v>
+        <v>0.08037601719060603</v>
       </c>
       <c r="W69">
-        <v>0.2165644595516261</v>
+        <v>0.2168473351464551</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3263026369529081</v>
+        <v>0.3215040687624241</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1974706998553082</v>
+        <v>0.1993706998553082</v>
       </c>
       <c r="C70">
-        <v>-192.0364611684483</v>
+        <v>-198.2460701697863</v>
       </c>
       <c r="D70">
-        <v>101.5675388315516</v>
+        <v>100.3109298302137</v>
       </c>
       <c r="E70">
-        <v>-35.596</v>
+        <v>-30.64299999999997</v>
       </c>
       <c r="F70">
-        <v>336.804</v>
+        <v>341.757</v>
       </c>
       <c r="G70">
         <v>43.2</v>
@@ -7027,37 +7027,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M70">
-        <v>79.41838319999999</v>
+        <v>80.5863006</v>
       </c>
       <c r="N70">
-        <v>-53.88504986666665</v>
+        <v>-55.05296726666666</v>
       </c>
       <c r="O70">
-        <v>-13.47126246666666</v>
+        <v>-13.76324181666666</v>
       </c>
       <c r="P70">
-        <v>-40.41378739999999</v>
+        <v>-41.28972544999999</v>
       </c>
       <c r="Q70">
-        <v>14.38621260000001</v>
+        <v>13.51027455000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1562953498616211</v>
+        <v>0.1598597159861895</v>
       </c>
       <c r="T70">
-        <v>1.709327920626993</v>
+        <v>1.764467530969799</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08037601719060603</v>
+        <v>0.07921114737624942</v>
       </c>
       <c r="W70">
-        <v>0.2168473351464551</v>
+        <v>0.2171220114486804</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3215040687624241</v>
+        <v>0.3168445895049976</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1993706998553082</v>
+        <v>0.2012706998553082</v>
       </c>
       <c r="C71">
-        <v>-198.2460701697863</v>
+        <v>-204.4249652539069</v>
       </c>
       <c r="D71">
-        <v>100.3109298302137</v>
+        <v>99.08503474609311</v>
       </c>
       <c r="E71">
-        <v>-30.64299999999997</v>
+        <v>-25.69</v>
       </c>
       <c r="F71">
-        <v>341.757</v>
+        <v>346.71</v>
       </c>
       <c r="G71">
         <v>43.2</v>
@@ -7109,37 +7109,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M71">
-        <v>80.5863006</v>
+        <v>81.75421799999999</v>
       </c>
       <c r="N71">
-        <v>-55.05296726666666</v>
+        <v>-56.22088466666665</v>
       </c>
       <c r="O71">
-        <v>-13.76324181666666</v>
+        <v>-14.05522116666666</v>
       </c>
       <c r="P71">
-        <v>-41.28972544999999</v>
+        <v>-42.16566349999999</v>
       </c>
       <c r="Q71">
-        <v>13.51027455000001</v>
+        <v>12.63433650000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1598597159861895</v>
+        <v>0.1636617065190625</v>
       </c>
       <c r="T71">
-        <v>1.764467530969799</v>
+        <v>1.823283115335459</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07921114737624942</v>
+        <v>0.07807955955658871</v>
       </c>
       <c r="W71">
-        <v>0.2171220114486804</v>
+        <v>0.2173888398565564</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3168445895049976</v>
+        <v>0.3123182382263548</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2012706998553082</v>
+        <v>0.2031706998553083</v>
       </c>
       <c r="C72">
-        <v>-204.4249652539069</v>
+        <v>-210.5742588853813</v>
       </c>
       <c r="D72">
-        <v>99.08503474609311</v>
+        <v>97.8887411146187</v>
       </c>
       <c r="E72">
-        <v>-25.69</v>
+        <v>-20.73699999999997</v>
       </c>
       <c r="F72">
-        <v>346.71</v>
+        <v>351.663</v>
       </c>
       <c r="G72">
         <v>43.2</v>
@@ -7191,37 +7191,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M72">
-        <v>81.75421799999999</v>
+        <v>82.9221354</v>
       </c>
       <c r="N72">
-        <v>-56.22088466666665</v>
+        <v>-57.38880206666666</v>
       </c>
       <c r="O72">
-        <v>-14.05522116666666</v>
+        <v>-14.34720051666666</v>
       </c>
       <c r="P72">
-        <v>-42.16566349999999</v>
+        <v>-43.04160155</v>
       </c>
       <c r="Q72">
-        <v>12.63433650000001</v>
+        <v>11.75839845</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1636617065190625</v>
+        <v>0.1677259032955819</v>
       </c>
       <c r="T72">
-        <v>1.823283115335459</v>
+        <v>1.886154946898751</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07807955955658871</v>
+        <v>0.07697984745015787</v>
       </c>
       <c r="W72">
-        <v>0.2173888398565564</v>
+        <v>0.2176481519712528</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3123182382263548</v>
+        <v>0.3079193898006315</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2031706998553082</v>
+        <v>0.2050706998553082</v>
       </c>
       <c r="C73">
-        <v>-210.5742588853813</v>
+        <v>-216.6950104447499</v>
       </c>
       <c r="D73">
-        <v>97.8887411146187</v>
+        <v>96.72098955525001</v>
       </c>
       <c r="E73">
-        <v>-20.73700000000002</v>
+        <v>-15.78400000000005</v>
       </c>
       <c r="F73">
-        <v>351.663</v>
+        <v>356.6159999999999</v>
       </c>
       <c r="G73">
         <v>43.2</v>
@@ -7273,37 +7273,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M73">
-        <v>82.92213539999999</v>
+        <v>84.09005279999998</v>
       </c>
       <c r="N73">
-        <v>-57.38880206666664</v>
+        <v>-58.55671946666664</v>
       </c>
       <c r="O73">
-        <v>-14.34720051666666</v>
+        <v>-14.63917986666666</v>
       </c>
       <c r="P73">
-        <v>-43.04160154999998</v>
+        <v>-43.91753959999998</v>
       </c>
       <c r="Q73">
-        <v>11.75839845000002</v>
+        <v>10.88246040000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1677259032955819</v>
+        <v>0.1720803998418526</v>
       </c>
       <c r="T73">
-        <v>1.886154946898751</v>
+        <v>1.953517623573706</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07697984745015789</v>
+        <v>0.07591068290223904</v>
       </c>
       <c r="W73">
-        <v>0.2176481519712528</v>
+        <v>0.217900260971652</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3079193898006316</v>
+        <v>0.3036427316089562</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2050706998553082</v>
+        <v>0.2069706998553082</v>
       </c>
       <c r="C74">
-        <v>-216.6950104447499</v>
+        <v>-222.7882293574924</v>
       </c>
       <c r="D74">
-        <v>96.72098955525001</v>
+        <v>95.58077064250752</v>
       </c>
       <c r="E74">
-        <v>-15.78400000000005</v>
+        <v>-10.83100000000002</v>
       </c>
       <c r="F74">
-        <v>356.6159999999999</v>
+        <v>361.569</v>
       </c>
       <c r="G74">
         <v>43.2</v>
@@ -7355,37 +7355,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M74">
-        <v>84.09005279999998</v>
+        <v>85.25797019999999</v>
       </c>
       <c r="N74">
-        <v>-58.55671946666664</v>
+        <v>-59.72463686666664</v>
       </c>
       <c r="O74">
-        <v>-14.63917986666666</v>
+        <v>-14.93115921666666</v>
       </c>
       <c r="P74">
-        <v>-43.91753959999998</v>
+        <v>-44.79347764999999</v>
       </c>
       <c r="Q74">
-        <v>10.88246040000002</v>
+        <v>10.00652235000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1720803998418526</v>
+        <v>0.1767574516878472</v>
       </c>
       <c r="T74">
-        <v>1.953517623573706</v>
+        <v>2.02587012815051</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07591068290223904</v>
+        <v>0.07487081053371521</v>
       </c>
       <c r="W74">
-        <v>0.217900260971652</v>
+        <v>0.2181454628761499</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3036427316089562</v>
+        <v>0.2994832421348609</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2069706998553082</v>
+        <v>0.2088706998553082</v>
       </c>
       <c r="C75">
-        <v>-222.7882293574924</v>
+        <v>-228.8548780042567</v>
       </c>
       <c r="D75">
-        <v>95.58077064250752</v>
+        <v>94.46712199574326</v>
       </c>
       <c r="E75">
-        <v>-10.83100000000002</v>
+        <v>-5.878000000000043</v>
       </c>
       <c r="F75">
-        <v>361.569</v>
+        <v>366.5219999999999</v>
       </c>
       <c r="G75">
         <v>43.2</v>
@@ -7437,37 +7437,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M75">
-        <v>85.25797019999999</v>
+        <v>86.42588759999998</v>
       </c>
       <c r="N75">
-        <v>-59.72463686666664</v>
+        <v>-60.89255426666664</v>
       </c>
       <c r="O75">
-        <v>-14.93115921666666</v>
+        <v>-15.22313856666666</v>
       </c>
       <c r="P75">
-        <v>-44.79347764999999</v>
+        <v>-45.66941569999997</v>
       </c>
       <c r="Q75">
-        <v>10.00652235000001</v>
+        <v>9.130584300000024</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1767574516878472</v>
+        <v>0.1817942767527644</v>
       </c>
       <c r="T75">
-        <v>2.02587012815051</v>
+        <v>2.103788210002453</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07487081053371521</v>
+        <v>0.07385904282380014</v>
       </c>
       <c r="W75">
-        <v>0.2181454628761499</v>
+        <v>0.2183840377021479</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2994832421348609</v>
+        <v>0.2954361712952006</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2088706998553082</v>
+        <v>0.2107706998553082</v>
       </c>
       <c r="C76">
-        <v>-228.8548780042567</v>
+        <v>-234.8958744299817</v>
       </c>
       <c r="D76">
-        <v>94.46712199574326</v>
+        <v>93.3791255700183</v>
       </c>
       <c r="E76">
-        <v>-5.878000000000043</v>
+        <v>-0.9250000000000114</v>
       </c>
       <c r="F76">
-        <v>366.5219999999999</v>
+        <v>371.475</v>
       </c>
       <c r="G76">
         <v>43.2</v>
@@ -7519,37 +7519,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M76">
-        <v>86.42588759999998</v>
+        <v>87.59380499999999</v>
       </c>
       <c r="N76">
-        <v>-60.89255426666664</v>
+        <v>-62.06047166666664</v>
       </c>
       <c r="O76">
-        <v>-15.22313856666666</v>
+        <v>-15.51511791666666</v>
       </c>
       <c r="P76">
-        <v>-45.66941569999997</v>
+        <v>-46.54535374999998</v>
       </c>
       <c r="Q76">
-        <v>9.130584300000024</v>
+        <v>8.254646250000015</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1817942767527644</v>
+        <v>0.187234047822875</v>
       </c>
       <c r="T76">
-        <v>2.103788210002453</v>
+        <v>2.187939738402551</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07385904282380014</v>
+        <v>0.07287425558614946</v>
       </c>
       <c r="W76">
-        <v>0.2183840377021479</v>
+        <v>0.218616250532786</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2954361712952006</v>
+        <v>0.2914970223445978</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2107706998553082</v>
+        <v>0.2126706998553082</v>
       </c>
       <c r="C77">
-        <v>-234.8958744299817</v>
+        <v>-240.9120948679428</v>
       </c>
       <c r="D77">
-        <v>93.3791255700183</v>
+        <v>92.31590513205721</v>
       </c>
       <c r="E77">
-        <v>-0.9250000000000114</v>
+        <v>4.02800000000002</v>
       </c>
       <c r="F77">
-        <v>371.475</v>
+        <v>376.428</v>
       </c>
       <c r="G77">
         <v>43.2</v>
@@ -7601,37 +7601,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M77">
-        <v>87.59380499999999</v>
+        <v>88.7617224</v>
       </c>
       <c r="N77">
-        <v>-62.06047166666664</v>
+        <v>-63.22838906666665</v>
       </c>
       <c r="O77">
-        <v>-15.51511791666666</v>
+        <v>-15.80709726666666</v>
       </c>
       <c r="P77">
-        <v>-46.54535374999998</v>
+        <v>-47.42129179999999</v>
       </c>
       <c r="Q77">
-        <v>8.254646250000015</v>
+        <v>7.378708200000005</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.187234047822875</v>
+        <v>0.1931271331488281</v>
       </c>
       <c r="T77">
-        <v>2.187939738402551</v>
+        <v>2.279103894169324</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07287425558614946</v>
+        <v>0.07191538380212117</v>
       </c>
       <c r="W77">
-        <v>0.218616250532786</v>
+        <v>0.2188423524994599</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2914970223445978</v>
+        <v>0.2876615352084847</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2126706998553082</v>
+        <v>0.2145706998553082</v>
       </c>
       <c r="C78">
-        <v>-240.9120948679428</v>
+        <v>-246.9043760933052</v>
       </c>
       <c r="D78">
-        <v>92.31590513205721</v>
+        <v>91.27662390669477</v>
       </c>
       <c r="E78">
-        <v>4.02800000000002</v>
+        <v>8.980999999999995</v>
       </c>
       <c r="F78">
-        <v>376.428</v>
+        <v>381.381</v>
       </c>
       <c r="G78">
         <v>43.2</v>
@@ -7683,37 +7683,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M78">
-        <v>88.7617224</v>
+        <v>89.9296398</v>
       </c>
       <c r="N78">
-        <v>-63.22838906666665</v>
+        <v>-64.39630646666666</v>
       </c>
       <c r="O78">
-        <v>-15.80709726666666</v>
+        <v>-16.09907661666666</v>
       </c>
       <c r="P78">
-        <v>-47.42129179999999</v>
+        <v>-48.29722984999999</v>
       </c>
       <c r="Q78">
-        <v>7.378708200000005</v>
+        <v>6.502770150000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1931271331488281</v>
+        <v>0.199532660677038</v>
       </c>
       <c r="T78">
-        <v>2.279103894169324</v>
+        <v>2.378195367828859</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07191538380212117</v>
+        <v>0.070981417778717</v>
       </c>
       <c r="W78">
-        <v>0.2188423524994599</v>
+        <v>0.2190625816877785</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2876615352084847</v>
+        <v>0.283925671114868</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2145706998553082</v>
+        <v>0.2164706998553082</v>
       </c>
       <c r="C79">
-        <v>-246.9043760933052</v>
+        <v>-252.8735176194708</v>
       </c>
       <c r="D79">
-        <v>91.27662390669477</v>
+        <v>90.26048238052917</v>
       </c>
       <c r="E79">
-        <v>8.980999999999995</v>
+        <v>13.93400000000003</v>
       </c>
       <c r="F79">
-        <v>381.381</v>
+        <v>386.334</v>
       </c>
       <c r="G79">
         <v>43.2</v>
@@ -7765,37 +7765,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M79">
-        <v>89.9296398</v>
+        <v>91.09755720000001</v>
       </c>
       <c r="N79">
-        <v>-64.39630646666666</v>
+        <v>-65.56422386666667</v>
       </c>
       <c r="O79">
-        <v>-16.09907661666666</v>
+        <v>-16.39105596666667</v>
       </c>
       <c r="P79">
-        <v>-48.29722984999999</v>
+        <v>-49.1731679</v>
       </c>
       <c r="Q79">
-        <v>6.502770150000003</v>
+        <v>5.626832100000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.199532660677038</v>
+        <v>0.2065205088896307</v>
       </c>
       <c r="T79">
-        <v>2.378195367828859</v>
+        <v>2.486295157275626</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.070981417778717</v>
+        <v>0.07007139960206678</v>
       </c>
       <c r="W79">
-        <v>0.2190625816877785</v>
+        <v>0.2192771639738327</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.283925671114868</v>
+        <v>0.2802855984082672</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2164706998553082</v>
+        <v>0.2183706998553082</v>
       </c>
       <c r="C80">
-        <v>-252.8735176194708</v>
+        <v>-258.8202837493341</v>
       </c>
       <c r="D80">
-        <v>90.26048238052917</v>
+        <v>89.26671625066587</v>
       </c>
       <c r="E80">
-        <v>13.93400000000003</v>
+        <v>18.887</v>
       </c>
       <c r="F80">
-        <v>386.334</v>
+        <v>391.287</v>
       </c>
       <c r="G80">
         <v>43.2</v>
@@ -7847,37 +7847,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M80">
-        <v>91.09755720000001</v>
+        <v>92.2654746</v>
       </c>
       <c r="N80">
-        <v>-65.56422386666667</v>
+        <v>-66.73214126666666</v>
       </c>
       <c r="O80">
-        <v>-16.39105596666667</v>
+        <v>-16.68303531666666</v>
       </c>
       <c r="P80">
-        <v>-49.1731679</v>
+        <v>-50.04910595</v>
       </c>
       <c r="Q80">
-        <v>5.626832100000001</v>
+        <v>4.750894049999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2065205088896307</v>
+        <v>0.2141738664558036</v>
       </c>
       <c r="T80">
-        <v>2.486295157275626</v>
+        <v>2.604690164764942</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07007139960206678</v>
+        <v>0.06918441986026846</v>
       </c>
       <c r="W80">
-        <v>0.2192771639738327</v>
+        <v>0.2194863137969487</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2802855984082672</v>
+        <v>0.2767376794410739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2183706998553082</v>
+        <v>0.2202706998553082</v>
       </c>
       <c r="C81">
-        <v>-258.8202837493341</v>
+        <v>-264.7454054925089</v>
       </c>
       <c r="D81">
-        <v>89.26671625066587</v>
+        <v>88.29459450749111</v>
       </c>
       <c r="E81">
-        <v>18.887</v>
+        <v>23.84000000000003</v>
       </c>
       <c r="F81">
-        <v>391.287</v>
+        <v>396.24</v>
       </c>
       <c r="G81">
         <v>43.2</v>
@@ -7929,37 +7929,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M81">
-        <v>92.2654746</v>
+        <v>93.43339200000001</v>
       </c>
       <c r="N81">
-        <v>-66.73214126666666</v>
+        <v>-67.90005866666667</v>
       </c>
       <c r="O81">
-        <v>-16.68303531666666</v>
+        <v>-16.97501466666667</v>
       </c>
       <c r="P81">
-        <v>-50.04910595</v>
+        <v>-50.925044</v>
       </c>
       <c r="Q81">
-        <v>4.750894049999999</v>
+        <v>3.874955999999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2141738664558036</v>
+        <v>0.2225925597785938</v>
       </c>
       <c r="T81">
-        <v>2.604690164764942</v>
+        <v>2.734924673003189</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06918441986026846</v>
+        <v>0.06831961461201511</v>
       </c>
       <c r="W81">
-        <v>0.2194863137969487</v>
+        <v>0.2196902348744869</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2767376794410739</v>
+        <v>0.2732784584480604</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2202706998553082</v>
+        <v>0.2221706998553082</v>
       </c>
       <c r="C82">
-        <v>-264.7454054925089</v>
+        <v>-270.6495823586316</v>
       </c>
       <c r="D82">
-        <v>88.29459450749111</v>
+        <v>87.34341764136843</v>
       </c>
       <c r="E82">
-        <v>23.84000000000003</v>
+        <v>28.79300000000001</v>
       </c>
       <c r="F82">
-        <v>396.24</v>
+        <v>401.193</v>
       </c>
       <c r="G82">
         <v>43.2</v>
@@ -8011,37 +8011,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M82">
-        <v>93.43339200000001</v>
+        <v>94.60130940000001</v>
       </c>
       <c r="N82">
-        <v>-67.90005866666667</v>
+        <v>-69.06797606666666</v>
       </c>
       <c r="O82">
-        <v>-16.97501466666667</v>
+        <v>-17.26699401666666</v>
       </c>
       <c r="P82">
-        <v>-50.925044</v>
+        <v>-51.80098204999999</v>
       </c>
       <c r="Q82">
-        <v>3.874955999999997</v>
+        <v>2.999017950000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2225925597785938</v>
+        <v>0.2318974313458882</v>
       </c>
       <c r="T82">
-        <v>2.734924673003189</v>
+        <v>2.878868076845462</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06831961461201511</v>
+        <v>0.06747616257976802</v>
       </c>
       <c r="W82">
-        <v>0.2196902348744869</v>
+        <v>0.2198891208636907</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2732784584480604</v>
+        <v>0.2699046503190721</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2221706998553082</v>
+        <v>0.2240706998553083</v>
       </c>
       <c r="C83">
-        <v>-270.6495823586316</v>
+        <v>-276.5334840359868</v>
       </c>
       <c r="D83">
-        <v>87.34341764136843</v>
+        <v>86.4125159640132</v>
       </c>
       <c r="E83">
-        <v>28.79300000000001</v>
+        <v>33.74600000000004</v>
       </c>
       <c r="F83">
-        <v>401.193</v>
+        <v>406.146</v>
       </c>
       <c r="G83">
         <v>43.2</v>
@@ -8093,37 +8093,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M83">
-        <v>94.60130940000001</v>
+        <v>95.76922680000001</v>
       </c>
       <c r="N83">
-        <v>-69.06797606666666</v>
+        <v>-70.23589346666667</v>
       </c>
       <c r="O83">
-        <v>-17.26699401666666</v>
+        <v>-17.55897336666667</v>
       </c>
       <c r="P83">
-        <v>-51.80098204999999</v>
+        <v>-52.6769201</v>
       </c>
       <c r="Q83">
-        <v>2.999017950000002</v>
+        <v>2.123079899999993</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2318974313458882</v>
+        <v>0.2422361775317709</v>
       </c>
       <c r="T83">
-        <v>2.878868076845462</v>
+        <v>3.038805192225766</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06747616257976802</v>
+        <v>0.06665328254830742</v>
       </c>
       <c r="W83">
-        <v>0.2198891208636907</v>
+        <v>0.2200831559751091</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2699046503190721</v>
+        <v>0.2666131301932297</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2240706998553083</v>
+        <v>0.2259706998553082</v>
       </c>
       <c r="C84">
-        <v>-276.5334840359868</v>
+        <v>-282.3977519639211</v>
       </c>
       <c r="D84">
-        <v>86.4125159640132</v>
+        <v>85.50124803607888</v>
       </c>
       <c r="E84">
-        <v>33.74600000000004</v>
+        <v>38.69900000000001</v>
       </c>
       <c r="F84">
-        <v>406.146</v>
+        <v>411.099</v>
       </c>
       <c r="G84">
         <v>43.2</v>
@@ -8175,37 +8175,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M84">
-        <v>95.76922680000001</v>
+        <v>96.93714420000001</v>
       </c>
       <c r="N84">
-        <v>-70.23589346666667</v>
+        <v>-71.40381086666666</v>
       </c>
       <c r="O84">
-        <v>-17.55897336666667</v>
+        <v>-17.85095271666667</v>
       </c>
       <c r="P84">
-        <v>-52.6769201</v>
+        <v>-53.55285814999999</v>
       </c>
       <c r="Q84">
-        <v>2.123079899999993</v>
+        <v>1.247141850000006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2422361775317709</v>
+        <v>0.2537912467983456</v>
       </c>
       <c r="T84">
-        <v>3.038805192225766</v>
+        <v>3.217558438827282</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06665328254830742</v>
+        <v>0.06585023095133986</v>
       </c>
       <c r="W84">
-        <v>0.2200831559751091</v>
+        <v>0.2202725155416741</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2666131301932297</v>
+        <v>0.2634009238053595</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2259706998553082</v>
+        <v>0.2278706998553082</v>
       </c>
       <c r="C85">
-        <v>-282.3977519639211</v>
+        <v>-288.2430008068028</v>
       </c>
       <c r="D85">
-        <v>85.50124803607888</v>
+        <v>84.60899919319723</v>
       </c>
       <c r="E85">
-        <v>38.69900000000001</v>
+        <v>43.65200000000004</v>
       </c>
       <c r="F85">
-        <v>411.099</v>
+        <v>416.052</v>
       </c>
       <c r="G85">
         <v>43.2</v>
@@ -8257,37 +8257,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M85">
-        <v>96.93714420000001</v>
+        <v>98.10506160000001</v>
       </c>
       <c r="N85">
-        <v>-71.40381086666666</v>
+        <v>-72.57172826666667</v>
       </c>
       <c r="O85">
-        <v>-17.85095271666667</v>
+        <v>-18.14293206666667</v>
       </c>
       <c r="P85">
-        <v>-53.55285814999999</v>
+        <v>-54.4287962</v>
       </c>
       <c r="Q85">
-        <v>1.247141850000006</v>
+        <v>0.3712037999999964</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2537912467983456</v>
+        <v>0.2667906997232423</v>
       </c>
       <c r="T85">
-        <v>3.217558438827282</v>
+        <v>3.418655841253988</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06585023095133986</v>
+        <v>0.06506629963049058</v>
       </c>
       <c r="W85">
-        <v>0.2202725155416741</v>
+        <v>0.2204573665471303</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2634009238053595</v>
+        <v>0.2602651985219623</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2278706998553082</v>
+        <v>0.2297706998553082</v>
       </c>
       <c r="C86">
-        <v>-288.2430008068027</v>
+        <v>-294.0698198366455</v>
       </c>
       <c r="D86">
-        <v>84.60899919319723</v>
+        <v>83.73518016335439</v>
       </c>
       <c r="E86">
-        <v>43.65199999999999</v>
+        <v>48.60499999999996</v>
       </c>
       <c r="F86">
-        <v>416.052</v>
+        <v>421.0049999999999</v>
       </c>
       <c r="G86">
         <v>43.2</v>
@@ -8339,37 +8339,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M86">
-        <v>98.1050616</v>
+        <v>99.27297899999999</v>
       </c>
       <c r="N86">
-        <v>-72.57172826666665</v>
+        <v>-73.73964566666665</v>
       </c>
       <c r="O86">
-        <v>-18.14293206666666</v>
+        <v>-18.43491141666666</v>
       </c>
       <c r="P86">
-        <v>-54.42879619999999</v>
+        <v>-55.30473424999998</v>
       </c>
       <c r="Q86">
-        <v>0.3712038000000035</v>
+        <v>-0.5047342499999843</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2667906997232421</v>
+        <v>0.2815234130381249</v>
       </c>
       <c r="T86">
-        <v>3.418655841253985</v>
+        <v>3.646566230670918</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06506629963049058</v>
+        <v>0.06430081375248482</v>
       </c>
       <c r="W86">
-        <v>0.2204573665471303</v>
+        <v>0.2206378681171641</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2602651985219624</v>
+        <v>0.2572032550099392</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2297706998553082</v>
+        <v>0.2316706998553082</v>
       </c>
       <c r="C87">
-        <v>-294.0698198366455</v>
+        <v>-299.8787742309327</v>
       </c>
       <c r="D87">
-        <v>83.73518016335439</v>
+        <v>82.87922576906728</v>
       </c>
       <c r="E87">
-        <v>48.60499999999996</v>
+        <v>53.55799999999999</v>
       </c>
       <c r="F87">
-        <v>421.0049999999999</v>
+        <v>425.958</v>
       </c>
       <c r="G87">
         <v>43.2</v>
@@ -8421,37 +8421,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M87">
-        <v>99.27297899999999</v>
+        <v>100.4408964</v>
       </c>
       <c r="N87">
-        <v>-73.73964566666665</v>
+        <v>-74.90756306666665</v>
       </c>
       <c r="O87">
-        <v>-18.43491141666666</v>
+        <v>-18.72689076666666</v>
       </c>
       <c r="P87">
-        <v>-55.30473424999998</v>
+        <v>-56.18067229999999</v>
       </c>
       <c r="Q87">
-        <v>-0.5047342499999843</v>
+        <v>-1.380672299999993</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2815234130381249</v>
+        <v>0.2983607996837053</v>
       </c>
       <c r="T87">
-        <v>3.646566230670918</v>
+        <v>3.907035247147411</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06430081375248482</v>
+        <v>0.06355312987164197</v>
       </c>
       <c r="W87">
-        <v>0.2206378681171641</v>
+        <v>0.2208141719762668</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2572032550099392</v>
+        <v>0.2542125194865679</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2316706998553082</v>
+        <v>0.2335706998553082</v>
       </c>
       <c r="C88">
-        <v>-299.8787742309327</v>
+        <v>-305.6704062916459</v>
       </c>
       <c r="D88">
-        <v>82.87922576906728</v>
+        <v>82.04059370835402</v>
       </c>
       <c r="E88">
-        <v>53.55799999999999</v>
+        <v>58.51099999999997</v>
       </c>
       <c r="F88">
-        <v>425.958</v>
+        <v>430.9109999999999</v>
       </c>
       <c r="G88">
         <v>43.2</v>
@@ -8503,37 +8503,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M88">
-        <v>100.4408964</v>
+        <v>101.6088138</v>
       </c>
       <c r="N88">
-        <v>-74.90756306666665</v>
+        <v>-76.07548046666665</v>
       </c>
       <c r="O88">
-        <v>-18.72689076666666</v>
+        <v>-19.01887011666666</v>
       </c>
       <c r="P88">
-        <v>-56.18067229999999</v>
+        <v>-57.05661034999999</v>
       </c>
       <c r="Q88">
-        <v>-1.380672299999993</v>
+        <v>-2.256610349999988</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2983607996837053</v>
+        <v>0.3177885535055288</v>
       </c>
       <c r="T88">
-        <v>3.907035247147411</v>
+        <v>4.207576420004905</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06355312987164197</v>
+        <v>0.06282263412599091</v>
       </c>
       <c r="W88">
-        <v>0.2208141719762668</v>
+        <v>0.2209864228730914</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2542125194865679</v>
+        <v>0.2512905365039637</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2335706998553082</v>
+        <v>0.2354706998553082</v>
       </c>
       <c r="C89">
-        <v>-305.6704062916459</v>
+        <v>-311.4452365910269</v>
       </c>
       <c r="D89">
-        <v>82.04059370835402</v>
+        <v>81.2187634089731</v>
       </c>
       <c r="E89">
-        <v>58.51099999999997</v>
+        <v>63.464</v>
       </c>
       <c r="F89">
-        <v>430.9109999999999</v>
+        <v>435.864</v>
       </c>
       <c r="G89">
         <v>43.2</v>
@@ -8585,37 +8585,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M89">
-        <v>101.6088138</v>
+        <v>102.7767312</v>
       </c>
       <c r="N89">
-        <v>-76.07548046666665</v>
+        <v>-77.24339786666665</v>
       </c>
       <c r="O89">
-        <v>-19.01887011666666</v>
+        <v>-19.31084946666666</v>
       </c>
       <c r="P89">
-        <v>-57.05661034999999</v>
+        <v>-57.93254839999999</v>
       </c>
       <c r="Q89">
-        <v>-2.256610349999988</v>
+        <v>-3.13254839999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3177885535055288</v>
+        <v>0.3404542662976562</v>
       </c>
       <c r="T89">
-        <v>4.207576420004905</v>
+        <v>4.558207788338648</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06282263412599091</v>
+        <v>0.06210874055637738</v>
       </c>
       <c r="W89">
-        <v>0.2209864228730914</v>
+        <v>0.2211547589768062</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2512905365039637</v>
+        <v>0.2484349622255095</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2354706998553082</v>
+        <v>0.2373706998553082</v>
       </c>
       <c r="C90">
-        <v>-311.4452365910269</v>
+        <v>-317.2037650491554</v>
       </c>
       <c r="D90">
-        <v>81.2187634089731</v>
+        <v>80.41323495084457</v>
       </c>
       <c r="E90">
-        <v>63.464</v>
+        <v>68.41699999999997</v>
       </c>
       <c r="F90">
-        <v>435.864</v>
+        <v>440.817</v>
       </c>
       <c r="G90">
         <v>43.2</v>
@@ -8667,37 +8667,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M90">
-        <v>102.7767312</v>
+        <v>103.9446486</v>
       </c>
       <c r="N90">
-        <v>-77.24339786666665</v>
+        <v>-78.41131526666665</v>
       </c>
       <c r="O90">
-        <v>-19.31084946666666</v>
+        <v>-19.60282881666666</v>
       </c>
       <c r="P90">
-        <v>-57.93254839999999</v>
+        <v>-58.80848644999999</v>
       </c>
       <c r="Q90">
-        <v>-3.13254839999999</v>
+        <v>-4.008486449999992</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3404542662976562</v>
+        <v>0.3672410177792613</v>
       </c>
       <c r="T90">
-        <v>4.558207788338648</v>
+        <v>4.972590314551252</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06210874055637738</v>
+        <v>0.06141088953889</v>
       </c>
       <c r="W90">
-        <v>0.2211547589768062</v>
+        <v>0.2213193122467298</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2484349622255095</v>
+        <v>0.2456435581555599</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2373706998553082</v>
+        <v>0.2392706998553082</v>
       </c>
       <c r="C91">
-        <v>-317.2037650491554</v>
+        <v>-322.9464719480339</v>
       </c>
       <c r="D91">
-        <v>80.41323495084457</v>
+        <v>79.62352805196602</v>
       </c>
       <c r="E91">
-        <v>68.41699999999997</v>
+        <v>73.37</v>
       </c>
       <c r="F91">
-        <v>440.817</v>
+        <v>445.77</v>
       </c>
       <c r="G91">
         <v>43.2</v>
@@ -8749,37 +8749,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M91">
-        <v>103.9446486</v>
+        <v>105.112566</v>
       </c>
       <c r="N91">
-        <v>-78.41131526666665</v>
+        <v>-79.57923266666666</v>
       </c>
       <c r="O91">
-        <v>-19.60282881666666</v>
+        <v>-19.89480816666666</v>
       </c>
       <c r="P91">
-        <v>-58.80848644999999</v>
+        <v>-59.68442449999999</v>
       </c>
       <c r="Q91">
-        <v>-4.008486449999992</v>
+        <v>-4.884424499999994</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3672410177792613</v>
+        <v>0.3993851195571875</v>
       </c>
       <c r="T91">
-        <v>4.972590314551252</v>
+        <v>5.469849346006378</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06141088953889</v>
+        <v>0.06072854632179121</v>
       </c>
       <c r="W91">
-        <v>0.2213193122467298</v>
+        <v>0.2214802087773216</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2456435581555599</v>
+        <v>0.2429141852871649</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2392706998553082</v>
+        <v>0.2411706998553082</v>
       </c>
       <c r="C92">
-        <v>-322.9464719480339</v>
+        <v>-328.673818886499</v>
       </c>
       <c r="D92">
-        <v>79.62352805196602</v>
+        <v>78.84918111350095</v>
       </c>
       <c r="E92">
-        <v>73.37</v>
+        <v>78.32299999999998</v>
       </c>
       <c r="F92">
-        <v>445.77</v>
+        <v>450.723</v>
       </c>
       <c r="G92">
         <v>43.2</v>
@@ -8831,37 +8831,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M92">
-        <v>105.112566</v>
+        <v>106.2804834</v>
       </c>
       <c r="N92">
-        <v>-79.57923266666666</v>
+        <v>-80.74715006666665</v>
       </c>
       <c r="O92">
-        <v>-19.89480816666666</v>
+        <v>-20.18678751666666</v>
       </c>
       <c r="P92">
-        <v>-59.68442449999999</v>
+        <v>-60.56036254999999</v>
       </c>
       <c r="Q92">
-        <v>-4.884424499999994</v>
+        <v>-5.760362549999989</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3993851195571875</v>
+        <v>0.4386723550635417</v>
       </c>
       <c r="T92">
-        <v>5.469849346006378</v>
+        <v>6.077610384451531</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06072854632179121</v>
+        <v>0.06006119965891439</v>
       </c>
       <c r="W92">
-        <v>0.2214802087773216</v>
+        <v>0.221637569120428</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2429141852871649</v>
+        <v>0.2402447986356576</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2411706998553082</v>
+        <v>0.2430706998553083</v>
       </c>
       <c r="C93">
-        <v>-328.673818886499</v>
+        <v>-334.3862496799495</v>
       </c>
       <c r="D93">
-        <v>78.84918111350095</v>
+        <v>78.08975032005044</v>
       </c>
       <c r="E93">
-        <v>78.32299999999998</v>
+        <v>83.27600000000001</v>
       </c>
       <c r="F93">
-        <v>450.723</v>
+        <v>455.676</v>
       </c>
       <c r="G93">
         <v>43.2</v>
@@ -8913,37 +8913,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M93">
-        <v>106.2804834</v>
+        <v>107.4484008</v>
       </c>
       <c r="N93">
-        <v>-80.74715006666665</v>
+        <v>-81.91506746666666</v>
       </c>
       <c r="O93">
-        <v>-20.18678751666666</v>
+        <v>-20.47876686666666</v>
       </c>
       <c r="P93">
-        <v>-60.56036254999999</v>
+        <v>-61.4363006</v>
       </c>
       <c r="Q93">
-        <v>-5.760362549999989</v>
+        <v>-6.636300599999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4386723550635417</v>
+        <v>0.4877813994464846</v>
       </c>
       <c r="T93">
-        <v>6.077610384451531</v>
+        <v>6.837311682507975</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06006119965891439</v>
+        <v>0.05940836053218706</v>
       </c>
       <c r="W93">
-        <v>0.221637569120428</v>
+        <v>0.2217915085865103</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2402447986356576</v>
+        <v>0.2376334421287483</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2430706998553083</v>
+        <v>0.2449706998553082</v>
       </c>
       <c r="C94">
-        <v>-334.3862496799495</v>
+        <v>-340.0841912085774</v>
       </c>
       <c r="D94">
-        <v>78.08975032005044</v>
+        <v>77.34480879142258</v>
       </c>
       <c r="E94">
-        <v>83.27600000000001</v>
+        <v>88.22899999999998</v>
       </c>
       <c r="F94">
-        <v>455.676</v>
+        <v>460.629</v>
       </c>
       <c r="G94">
         <v>43.2</v>
@@ -8995,37 +8995,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M94">
-        <v>107.4484008</v>
+        <v>108.6163182</v>
       </c>
       <c r="N94">
-        <v>-81.91506746666666</v>
+        <v>-83.08298486666665</v>
       </c>
       <c r="O94">
-        <v>-20.47876686666666</v>
+        <v>-20.77074621666666</v>
       </c>
       <c r="P94">
-        <v>-61.4363006</v>
+        <v>-62.31223864999998</v>
       </c>
       <c r="Q94">
-        <v>-6.636300599999998</v>
+        <v>-7.512238649999986</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4877813994464846</v>
+        <v>0.5509215993674109</v>
       </c>
       <c r="T94">
-        <v>6.837311682507975</v>
+        <v>7.814070494294829</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05940836053218706</v>
+        <v>0.05876956095657215</v>
       </c>
       <c r="W94">
-        <v>0.2217915085865103</v>
+        <v>0.2219421375264403</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2376334421287483</v>
+        <v>0.2350782438262886</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2449706998553082</v>
+        <v>0.2468706998553082</v>
       </c>
       <c r="C95">
-        <v>-340.0841912085774</v>
+        <v>-345.7680542175063</v>
       </c>
       <c r="D95">
-        <v>77.34480879142258</v>
+        <v>76.61394578249362</v>
       </c>
       <c r="E95">
-        <v>88.22899999999998</v>
+        <v>93.18200000000002</v>
       </c>
       <c r="F95">
-        <v>460.629</v>
+        <v>465.582</v>
       </c>
       <c r="G95">
         <v>43.2</v>
@@ -9077,37 +9077,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M95">
-        <v>108.6163182</v>
+        <v>109.7842356</v>
       </c>
       <c r="N95">
-        <v>-83.08298486666665</v>
+        <v>-84.25090226666666</v>
       </c>
       <c r="O95">
-        <v>-20.77074621666666</v>
+        <v>-21.06272556666666</v>
       </c>
       <c r="P95">
-        <v>-62.31223864999998</v>
+        <v>-63.18817669999999</v>
       </c>
       <c r="Q95">
-        <v>-7.512238649999986</v>
+        <v>-8.388176699999995</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5509215993674109</v>
+        <v>0.6351085325953129</v>
       </c>
       <c r="T95">
-        <v>7.814070494294829</v>
+        <v>9.116415576677303</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05876956095657215</v>
+        <v>0.05814435286128946</v>
       </c>
       <c r="W95">
-        <v>0.2219421375264403</v>
+        <v>0.2220895615953079</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2350782438262886</v>
+        <v>0.2325774114451579</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2468706998553082</v>
+        <v>0.2487706998553082</v>
       </c>
       <c r="C96">
-        <v>-345.7680542175063</v>
+        <v>-351.4382340719903</v>
       </c>
       <c r="D96">
-        <v>76.61394578249362</v>
+        <v>75.89676592800964</v>
       </c>
       <c r="E96">
-        <v>93.18200000000002</v>
+        <v>98.13499999999999</v>
       </c>
       <c r="F96">
-        <v>465.582</v>
+        <v>470.535</v>
       </c>
       <c r="G96">
         <v>43.2</v>
@@ -9159,37 +9159,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M96">
-        <v>109.7842356</v>
+        <v>110.952153</v>
       </c>
       <c r="N96">
-        <v>-84.25090226666666</v>
+        <v>-85.41881966666665</v>
       </c>
       <c r="O96">
-        <v>-21.06272556666666</v>
+        <v>-21.35470491666666</v>
       </c>
       <c r="P96">
-        <v>-63.18817669999999</v>
+        <v>-64.06411474999999</v>
       </c>
       <c r="Q96">
-        <v>-8.388176699999995</v>
+        <v>-9.26411474999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6351085325953129</v>
+        <v>0.7529702391143758</v>
       </c>
       <c r="T96">
-        <v>9.116415576677303</v>
+        <v>10.93969869201277</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05814435286128946</v>
+        <v>0.05753230704169694</v>
       </c>
       <c r="W96">
-        <v>0.2220895615953079</v>
+        <v>0.2222338819995679</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2325774114451579</v>
+        <v>0.2301292281667878</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2487706998553082</v>
+        <v>0.2506706998553083</v>
       </c>
       <c r="C97">
-        <v>-351.4382340719903</v>
+        <v>-357.0951114705889</v>
       </c>
       <c r="D97">
-        <v>75.89676592800964</v>
+        <v>75.19288852941108</v>
       </c>
       <c r="E97">
-        <v>98.13499999999999</v>
+        <v>103.088</v>
       </c>
       <c r="F97">
-        <v>470.535</v>
+        <v>475.488</v>
       </c>
       <c r="G97">
         <v>43.2</v>
@@ -9241,37 +9241,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M97">
-        <v>110.952153</v>
+        <v>112.1200704</v>
       </c>
       <c r="N97">
-        <v>-85.41881966666665</v>
+        <v>-86.58673706666666</v>
       </c>
       <c r="O97">
-        <v>-21.35470491666666</v>
+        <v>-21.64668426666666</v>
       </c>
       <c r="P97">
-        <v>-64.06411474999999</v>
+        <v>-64.94005279999999</v>
       </c>
       <c r="Q97">
-        <v>-9.26411474999999</v>
+        <v>-10.14005279999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7529702391143758</v>
+        <v>0.9297627988929703</v>
       </c>
       <c r="T97">
-        <v>10.93969869201277</v>
+        <v>13.67462336501597</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05753230704169694</v>
+        <v>0.05693301217667927</v>
       </c>
       <c r="W97">
-        <v>0.2222338819995679</v>
+        <v>0.222375195728739</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2301292281667878</v>
+        <v>0.227732048706717</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2506706998553082</v>
+        <v>0.2525706998553082</v>
       </c>
       <c r="C98">
-        <v>-357.0951114705888</v>
+        <v>-362.7390531190229</v>
       </c>
       <c r="D98">
-        <v>75.19288852941108</v>
+        <v>74.50194688097707</v>
       </c>
       <c r="E98">
-        <v>103.088</v>
+        <v>108.0409999999999</v>
       </c>
       <c r="F98">
-        <v>475.4879999999999</v>
+        <v>480.4409999999999</v>
       </c>
       <c r="G98">
         <v>43.2</v>
@@ -9323,37 +9323,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M98">
-        <v>112.1200704</v>
+        <v>113.2879878</v>
       </c>
       <c r="N98">
-        <v>-86.58673706666664</v>
+        <v>-87.75465446666664</v>
       </c>
       <c r="O98">
-        <v>-21.64668426666666</v>
+        <v>-21.93866361666666</v>
       </c>
       <c r="P98">
-        <v>-64.94005279999999</v>
+        <v>-65.81599084999998</v>
       </c>
       <c r="Q98">
-        <v>-10.14005279999999</v>
+        <v>-11.01599084999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.929762798892968</v>
+        <v>1.224417065190624</v>
       </c>
       <c r="T98">
-        <v>13.67462336501593</v>
+        <v>18.23283115335457</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05693301217667927</v>
+        <v>0.0563460739068166</v>
       </c>
       <c r="W98">
-        <v>0.222375195728739</v>
+        <v>0.2225135957727727</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.227732048706717</v>
+        <v>0.2253842956272664</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2525706998553082</v>
+        <v>0.2544706998553082</v>
       </c>
       <c r="C99">
-        <v>-362.7390531190229</v>
+        <v>-368.3704123672164</v>
       </c>
       <c r="D99">
-        <v>74.50194688097707</v>
+        <v>73.82358763278356</v>
       </c>
       <c r="E99">
-        <v>108.0409999999999</v>
+        <v>112.994</v>
       </c>
       <c r="F99">
-        <v>480.4409999999999</v>
+        <v>485.3939999999999</v>
       </c>
       <c r="G99">
         <v>43.2</v>
@@ -9405,37 +9405,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M99">
-        <v>113.2879878</v>
+        <v>114.4559052</v>
       </c>
       <c r="N99">
-        <v>-87.75465446666664</v>
+        <v>-88.92257186666664</v>
       </c>
       <c r="O99">
-        <v>-21.93866361666666</v>
+        <v>-22.23064296666666</v>
       </c>
       <c r="P99">
-        <v>-65.81599084999998</v>
+        <v>-66.69192889999998</v>
       </c>
       <c r="Q99">
-        <v>-11.01599084999998</v>
+        <v>-11.89192889999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.224417065190624</v>
+        <v>1.813725597785936</v>
       </c>
       <c r="T99">
-        <v>18.23283115335457</v>
+        <v>27.34924673003186</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0563460739068166</v>
+        <v>0.05577111396899194</v>
       </c>
       <c r="W99">
-        <v>0.2225135957727727</v>
+        <v>0.2226491713261117</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2253842956272664</v>
+        <v>0.2230844558759677</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2544706998553082</v>
+        <v>0.2563706998553082</v>
       </c>
       <c r="C100">
-        <v>-368.3704123672164</v>
+        <v>-373.9895298118497</v>
       </c>
       <c r="D100">
-        <v>73.82358763278356</v>
+        <v>73.15747018815019</v>
       </c>
       <c r="E100">
-        <v>112.994</v>
+        <v>117.9469999999999</v>
       </c>
       <c r="F100">
-        <v>485.3939999999999</v>
+        <v>490.3469999999999</v>
       </c>
       <c r="G100">
         <v>43.2</v>
@@ -9487,37 +9487,37 @@
         <v>25.53333333333335</v>
       </c>
       <c r="M100">
-        <v>114.4559052</v>
+        <v>115.6238226</v>
       </c>
       <c r="N100">
-        <v>-88.92257186666664</v>
+        <v>-90.09048926666664</v>
       </c>
       <c r="O100">
-        <v>-22.23064296666666</v>
+        <v>-22.52262231666666</v>
       </c>
       <c r="P100">
-        <v>-66.69192889999998</v>
+        <v>-67.56786694999998</v>
       </c>
       <c r="Q100">
-        <v>-11.89192889999998</v>
+        <v>-12.76786694999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.813725597785936</v>
+        <v>3.581651195571872</v>
       </c>
       <c r="T100">
-        <v>27.34924673003186</v>
+        <v>54.69849346006373</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05577111396899194</v>
+        <v>0.05520776938344657</v>
       </c>
       <c r="W100">
-        <v>0.2226491713261117</v>
+        <v>0.2227820079793833</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2230844558759677</v>
+        <v>0.2208310775337863</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2563706998553082</v>
-      </c>
-      <c r="C101">
-        <v>-373.9895298118497</v>
-      </c>
-      <c r="D101">
-        <v>73.15747018815019</v>
-      </c>
-      <c r="E101">
-        <v>117.9469999999999</v>
-      </c>
-      <c r="F101">
-        <v>490.3469999999999</v>
-      </c>
-      <c r="G101">
-        <v>43.2</v>
-      </c>
-      <c r="H101">
-        <v>122.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>80.33333333333334</v>
-      </c>
-      <c r="K101">
-        <v>54.8</v>
-      </c>
-      <c r="L101">
-        <v>25.53333333333335</v>
-      </c>
-      <c r="M101">
-        <v>115.6238226</v>
-      </c>
-      <c r="N101">
-        <v>-90.09048926666664</v>
-      </c>
-      <c r="O101">
-        <v>-22.52262231666666</v>
-      </c>
-      <c r="P101">
-        <v>-67.56786694999998</v>
-      </c>
-      <c r="Q101">
-        <v>-12.76786694999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.581651195571872</v>
-      </c>
-      <c r="T101">
-        <v>54.69849346006373</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05520776938344657</v>
-      </c>
-      <c r="W101">
-        <v>0.2227820079793833</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2208310775337863</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
